--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,369 +851,369 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14">
+        <v>3</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="14">
+        <v>11</v>
+      </c>
+      <c r="G14" s="14">
         <v>2</v>
       </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="14">
-        <v>5</v>
-      </c>
-      <c r="G14" s="14">
-        <v>5</v>
-      </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="I14" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J14" s="14">
         <v>10</v>
       </c>
       <c r="K14" s="15">
-        <v>-20</v>
+        <v>40</v>
       </c>
       <c r="L14" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N14" s="15">
-        <v>-84.615384615384</v>
+        <v>-77.049180327868</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D15" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="15">
-        <v>25</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F15" s="14">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G15" s="14">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H15" s="15">
-        <v>57.142857142857</v>
+        <v>17.073170731707</v>
       </c>
       <c r="I15" s="14">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="J15" s="14">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K15" s="15">
-        <v>32</v>
+        <v>22.950819672131</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>33.928571428571</v>
       </c>
       <c r="M15" s="15">
-        <v>112.903225806452</v>
+        <v>108.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>15.789473684210</v>
+        <v>15.384615384615</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D16" s="14">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E16" s="15">
-        <v>-9.333333333333</v>
+        <v>4.938271604938</v>
       </c>
       <c r="F16" s="14">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G16" s="14">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H16" s="15">
-        <v>-18.691588785046</v>
+        <v>-15.479876160990</v>
       </c>
       <c r="I16" s="14">
-        <v>380</v>
+        <v>464</v>
       </c>
       <c r="J16" s="14">
-        <v>447</v>
+        <v>528</v>
       </c>
       <c r="K16" s="15">
-        <v>-14.988814317673</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="L16" s="15">
-        <v>-31.407942238267</v>
+        <v>-24.183006535947</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.929203539823</v>
+        <v>-8.840864440078</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.120879120879</v>
+        <v>-77.988614800759</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D17" s="14">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="E17" s="15">
-        <v>-22.641509433962</v>
+        <v>11.194029850746</v>
       </c>
       <c r="F17" s="14">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="G17" s="14">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.909090909090</v>
+        <v>-3.760683760683</v>
       </c>
       <c r="I17" s="14">
-        <v>772</v>
+        <v>933</v>
       </c>
       <c r="J17" s="14">
-        <v>813</v>
+        <v>947</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.043050430504</v>
+        <v>-1.478352692713</v>
       </c>
       <c r="L17" s="15">
-        <v>1.445466491458</v>
+        <v>0.755939524838</v>
       </c>
       <c r="M17" s="15">
-        <v>87.378640776699</v>
+        <v>93.167701863354</v>
       </c>
       <c r="N17" s="15">
-        <v>-2.525252525252</v>
+        <v>3.322259136212</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D18" s="14">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="E18" s="15">
-        <v>-46.268656716417</v>
+        <v>15.555555555555</v>
       </c>
       <c r="F18" s="14">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="G18" s="14">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.6</v>
+        <v>-28.099173553719</v>
       </c>
       <c r="I18" s="14">
-        <v>246</v>
+        <v>301</v>
       </c>
       <c r="J18" s="14">
-        <v>325</v>
+        <v>370</v>
       </c>
       <c r="K18" s="15">
-        <v>-24.307692307692</v>
+        <v>-18.648648648648</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.463917525773</v>
+        <v>-11.209439528023</v>
       </c>
       <c r="M18" s="15">
-        <v>-34.224598930481</v>
+        <v>-27.817745803357</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.730673316708</v>
+        <v>-87.025862068965</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="D19" s="14">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="E19" s="15">
-        <v>-21.212121212121</v>
+        <v>5</v>
       </c>
       <c r="F19" s="14">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="G19" s="14">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="H19" s="15">
-        <v>-19.062027231467</v>
+        <v>-19.558359621451</v>
       </c>
       <c r="I19" s="14">
-        <v>740</v>
+        <v>895</v>
       </c>
       <c r="J19" s="14">
-        <v>881</v>
+        <v>1021</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.004540295119</v>
+        <v>-12.340842311459</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.165354330708</v>
+        <v>-23.569598633646</v>
       </c>
       <c r="M19" s="15">
-        <v>77.033492822966</v>
+        <v>86.847599164926</v>
       </c>
       <c r="N19" s="15">
-        <v>2.777777777777</v>
+        <v>8.091787439613</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="D20" s="14">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E20" s="15">
-        <v>14.473684210526</v>
+        <v>-28.169014084507</v>
       </c>
       <c r="F20" s="14">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="G20" s="14">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H20" s="15">
-        <v>-8.278145695364</v>
+        <v>-17.940199335548</v>
       </c>
       <c r="I20" s="14">
-        <v>364</v>
+        <v>411</v>
       </c>
       <c r="J20" s="14">
-        <v>417</v>
+        <v>488</v>
       </c>
       <c r="K20" s="15">
-        <v>-12.709832134292</v>
+        <v>-15.778688524590</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.935334872979</v>
+        <v>-22.306238185255</v>
       </c>
       <c r="M20" s="15">
-        <v>78.431372549019</v>
+        <v>71.966527196652</v>
       </c>
       <c r="N20" s="15">
-        <v>-78.242677824267</v>
+        <v>-78.825347758887</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="D21" s="17">
-        <v>556</v>
+        <v>482</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.446043165467</v>
+        <v>2.282157676348</v>
       </c>
       <c r="F21" s="17">
-        <v>1838</v>
+        <v>1826</v>
       </c>
       <c r="G21" s="17">
-        <v>2179</v>
+        <v>2128</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.649380449747</v>
+        <v>-14.191729323308</v>
       </c>
       <c r="I21" s="17">
-        <v>2576</v>
+        <v>3093</v>
       </c>
       <c r="J21" s="17">
-        <v>2943</v>
+        <v>3425</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.470268433571</v>
+        <v>-9.693430656934</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.197042751526</v>
+        <v>-15.190567589799</v>
       </c>
       <c r="M21" s="18">
-        <v>35.650342285413</v>
+        <v>42.468908337171</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.815142576204</v>
+        <v>-62.399708242159</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
         <v>10</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G22" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H22" s="15">
-        <v>28.571428571428</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I22" s="14">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="J22" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K22" s="15">
-        <v>34.285714285714</v>
+        <v>40</v>
       </c>
       <c r="L22" s="15">
-        <v>17.5</v>
+        <v>1.818181818181</v>
       </c>
       <c r="M22" s="15">
-        <v>51.612903225806</v>
+        <v>75</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D23" s="14">
         <v>24</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>29.166666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G23" s="14">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H23" s="15">
-        <v>-7.547169811320</v>
+        <v>-7.207207207207</v>
       </c>
       <c r="I23" s="14">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="J23" s="14">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="K23" s="15">
-        <v>-8.724832214765</v>
+        <v>-1.734104046242</v>
       </c>
       <c r="L23" s="15">
-        <v>-26.086956521739</v>
+        <v>-22.374429223744</v>
       </c>
       <c r="M23" s="15">
-        <v>38.775510204081</v>
+        <v>44.067796610169</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D24" s="14">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="E24" s="15">
-        <v>0.740740740740</v>
+        <v>-11.920529801324</v>
       </c>
       <c r="F24" s="14">
-        <v>1166</v>
+        <v>1077</v>
       </c>
       <c r="G24" s="14">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.971475142624</v>
+        <v>-11.793611793611</v>
       </c>
       <c r="I24" s="14">
-        <v>1629</v>
+        <v>1897</v>
       </c>
       <c r="J24" s="14">
-        <v>1685</v>
+        <v>1987</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.323442136498</v>
+        <v>-4.529441368897</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.380202474690</v>
+        <v>-9.451073985680</v>
       </c>
       <c r="M24" s="15">
-        <v>26.573426573426</v>
+        <v>30.288461538461</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="D25" s="14">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E25" s="15">
-        <v>-14.117647058823</v>
+        <v>10.869565217391</v>
       </c>
       <c r="F25" s="14">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="G25" s="14">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="H25" s="15">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="14">
-        <v>461</v>
+        <v>563</v>
       </c>
       <c r="J25" s="14">
-        <v>578</v>
+        <v>670</v>
       </c>
       <c r="K25" s="15">
-        <v>-20.242214532872</v>
+        <v>-15.970149253731</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.273885350318</v>
+        <v>-39.003250270855</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D26" s="14">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="E26" s="15">
-        <v>8.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F26" s="14">
-        <v>747</v>
+        <v>723</v>
       </c>
       <c r="G26" s="14">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="H26" s="15">
-        <v>8.104196816208</v>
+        <v>3.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>1046</v>
+        <v>1208</v>
       </c>
       <c r="J26" s="14">
-        <v>942</v>
+        <v>1140</v>
       </c>
       <c r="K26" s="15">
-        <v>11.040339702760</v>
+        <v>5.964912280701</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.413760603204</v>
+        <v>-6.501547987616</v>
       </c>
       <c r="M26" s="15">
-        <v>7.502569373072</v>
+        <v>5.779334500875</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D27" s="14">
         <v>15</v>
       </c>
       <c r="E27" s="15">
-        <v>6.666666666666</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F27" s="14">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G27" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H27" s="15">
-        <v>34.090909090909</v>
+        <v>12</v>
       </c>
       <c r="I27" s="14">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J27" s="14">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="K27" s="15">
-        <v>17.460317460317</v>
+        <v>10.256410256410</v>
       </c>
       <c r="L27" s="15">
-        <v>4.225352112676</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E28" s="15">
-        <v>290</v>
+        <v>25</v>
       </c>
       <c r="F28" s="14">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G28" s="14">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="H28" s="15">
-        <v>25.675675675675</v>
+        <v>60.655737704918</v>
       </c>
       <c r="I28" s="14">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="J28" s="14">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="K28" s="15">
-        <v>33.980582524271</v>
+        <v>29.411764705882</v>
       </c>
       <c r="L28" s="15">
-        <v>28.971962616822</v>
+        <v>28.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D29" s="14">
         <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="F29" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G29" s="14">
         <v>12</v>
       </c>
       <c r="H29" s="15">
-        <v>58.333333333333</v>
+        <v>75</v>
       </c>
       <c r="I29" s="14">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J29" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K29" s="15">
-        <v>26.086956521739</v>
+        <v>52</v>
       </c>
       <c r="L29" s="15">
-        <v>-14.705882352941</v>
+        <v>-24</v>
       </c>
       <c r="M29" s="15">
-        <v>-25.641025641025</v>
+        <v>-22.448979591836</v>
       </c>
       <c r="N29" s="15">
-        <v>-74.782608695652</v>
+        <v>-72.058823529411</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,13 +1508,13 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D30" s="14">
         <v>2</v>
       </c>
       <c r="E30" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F30" s="14">
         <v>15</v>
@@ -1526,63 +1526,63 @@
         <v>36.363636363636</v>
       </c>
       <c r="I30" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J30" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K30" s="15">
-        <v>26.315789473684</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L30" s="15">
-        <v>-17.241379310344</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.333333333333</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="N30" s="15">
-        <v>-77.358490566037</v>
+        <v>-75.409836065573</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>29</v>
+      <c r="C31" s="14">
+        <v>2</v>
+      </c>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>100</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>29</v>
+        <v>5</v>
+      </c>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>400</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>29</v>
+        <v>6</v>
+      </c>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>500</v>
       </c>
       <c r="L31" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,14 +1607,14 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
-      </c>
-      <c r="D33" s="14">
-        <v>2</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-50</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>2</v>
@@ -1626,22 +1626,22 @@
         <v>0</v>
       </c>
       <c r="I33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="14">
         <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L33" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>644</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>17862</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>9538</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>19326</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>8856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>22946</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>79825</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,369 +851,369 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>3</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>2</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" s="15">
-        <v>450</v>
+        <v>50</v>
       </c>
       <c r="I14" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K14" s="15">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="N14" s="15">
-        <v>-77.049180327868</v>
+        <v>-79.166666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D15" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" s="15">
-        <v>-45.454545454545</v>
+        <v>-10</v>
       </c>
       <c r="F15" s="14">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G15" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H15" s="15">
-        <v>17.073170731707</v>
+        <v>-6.976744186046</v>
       </c>
       <c r="I15" s="14">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J15" s="14">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="K15" s="15">
-        <v>22.950819672131</v>
+        <v>19.444444444444</v>
       </c>
       <c r="L15" s="15">
-        <v>33.928571428571</v>
+        <v>40.983606557377</v>
       </c>
       <c r="M15" s="15">
-        <v>108.333333333333</v>
+        <v>115</v>
       </c>
       <c r="N15" s="15">
-        <v>15.384615384615</v>
+        <v>17.808219178082</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D16" s="14">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="E16" s="15">
-        <v>4.938271604938</v>
+        <v>4.6875</v>
       </c>
       <c r="F16" s="14">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G16" s="14">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="H16" s="15">
-        <v>-15.479876160990</v>
+        <v>-9.446254071661</v>
       </c>
       <c r="I16" s="14">
-        <v>464</v>
+        <v>536</v>
       </c>
       <c r="J16" s="14">
-        <v>528</v>
+        <v>592</v>
       </c>
       <c r="K16" s="15">
-        <v>-12.121212121212</v>
+        <v>-9.459459459459</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.183006535947</v>
+        <v>-22.766570605187</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.840864440078</v>
+        <v>-7.745266781411</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.988614800759</v>
+        <v>-77.478991596638</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="D17" s="14">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E17" s="15">
-        <v>11.194029850746</v>
+        <v>16.216216216216</v>
       </c>
       <c r="F17" s="14">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="G17" s="14">
-        <v>585</v>
+        <v>560</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.760683760683</v>
+        <v>-0.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>933</v>
+        <v>1073</v>
       </c>
       <c r="J17" s="14">
-        <v>947</v>
+        <v>1058</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.478352692713</v>
+        <v>1.417769376181</v>
       </c>
       <c r="L17" s="15">
-        <v>0.755939524838</v>
+        <v>2.876318312559</v>
       </c>
       <c r="M17" s="15">
-        <v>93.167701863354</v>
+        <v>85</v>
       </c>
       <c r="N17" s="15">
-        <v>3.322259136212</v>
+        <v>3.471552555448</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="14">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="E18" s="15">
-        <v>15.555555555555</v>
+        <v>-24.285714285714</v>
       </c>
       <c r="F18" s="14">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G18" s="14">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H18" s="15">
-        <v>-28.099173553719</v>
+        <v>-27.049180327868</v>
       </c>
       <c r="I18" s="14">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="J18" s="14">
-        <v>370</v>
+        <v>440</v>
       </c>
       <c r="K18" s="15">
-        <v>-18.648648648648</v>
+        <v>-18.636363636363</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.209439528023</v>
+        <v>-12.469437652811</v>
       </c>
       <c r="M18" s="15">
-        <v>-27.817745803357</v>
+        <v>-23.010752688172</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.025862068965</v>
+        <v>-86.480362537764</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D19" s="14">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="E19" s="15">
-        <v>5</v>
+        <v>-4.848484848484</v>
       </c>
       <c r="F19" s="14">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="G19" s="14">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H19" s="15">
-        <v>-19.558359621451</v>
+        <v>-14.060031595576</v>
       </c>
       <c r="I19" s="14">
-        <v>895</v>
+        <v>1057</v>
       </c>
       <c r="J19" s="14">
-        <v>1021</v>
+        <v>1186</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.340842311459</v>
+        <v>-10.876897133220</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.569598633646</v>
+        <v>-20.166163141994</v>
       </c>
       <c r="M19" s="15">
-        <v>86.847599164926</v>
+        <v>90.794223826714</v>
       </c>
       <c r="N19" s="15">
-        <v>8.091787439613</v>
+        <v>11.733615221987</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D20" s="14">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20" s="15">
-        <v>-28.169014084507</v>
+        <v>-15.714285714285</v>
       </c>
       <c r="F20" s="14">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G20" s="14">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="H20" s="15">
-        <v>-17.940199335548</v>
+        <v>-15.593220338983</v>
       </c>
       <c r="I20" s="14">
-        <v>411</v>
+        <v>469</v>
       </c>
       <c r="J20" s="14">
-        <v>488</v>
+        <v>558</v>
       </c>
       <c r="K20" s="15">
-        <v>-15.778688524590</v>
+        <v>-15.949820788530</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.306238185255</v>
+        <v>-20.777027027027</v>
       </c>
       <c r="M20" s="15">
-        <v>71.966527196652</v>
+        <v>73.703703703703</v>
       </c>
       <c r="N20" s="15">
-        <v>-78.825347758887</v>
+        <v>-79.081177520071</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="D21" s="17">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E21" s="18">
-        <v>2.282157676348</v>
+        <v>-3.658536585365</v>
       </c>
       <c r="F21" s="17">
-        <v>1826</v>
+        <v>1851</v>
       </c>
       <c r="G21" s="17">
-        <v>2128</v>
+        <v>2086</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.191729323308</v>
+        <v>-11.265580057526</v>
       </c>
       <c r="I21" s="17">
-        <v>3093</v>
+        <v>3594</v>
       </c>
       <c r="J21" s="17">
-        <v>3425</v>
+        <v>3918</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.693430656934</v>
+        <v>-8.269525267993</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.190567589799</v>
+        <v>-13.146447559207</v>
       </c>
       <c r="M21" s="18">
-        <v>42.468908337171</v>
+        <v>43.645083932853</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.399708242159</v>
+        <v>-61.757820812938</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
         <v>10</v>
       </c>
       <c r="D22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F22" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G22" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H22" s="15">
-        <v>30.769230769230</v>
+        <v>60</v>
       </c>
       <c r="I22" s="14">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="J22" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K22" s="15">
-        <v>40</v>
+        <v>45.652173913043</v>
       </c>
       <c r="L22" s="15">
-        <v>1.818181818181</v>
+        <v>3.076923076923</v>
       </c>
       <c r="M22" s="15">
-        <v>75</v>
+        <v>97.058823529411</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D23" s="14">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E23" s="15">
-        <v>29.166666666666</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="F23" s="14">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G23" s="14">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="H23" s="15">
-        <v>-7.207207207207</v>
+        <v>-11.290322580645</v>
       </c>
       <c r="I23" s="14">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="J23" s="14">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="K23" s="15">
-        <v>-1.734104046242</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L23" s="15">
-        <v>-22.374429223744</v>
+        <v>-16.806722689075</v>
       </c>
       <c r="M23" s="15">
-        <v>44.067796610169</v>
+        <v>47.761194029850</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>266</v>
+        <v>313</v>
       </c>
       <c r="D24" s="14">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E24" s="15">
-        <v>-11.920529801324</v>
+        <v>-0.318471337579</v>
       </c>
       <c r="F24" s="14">
-        <v>1077</v>
+        <v>1120</v>
       </c>
       <c r="G24" s="14">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.793611793611</v>
+        <v>-8.045977011494</v>
       </c>
       <c r="I24" s="14">
-        <v>1897</v>
+        <v>2207</v>
       </c>
       <c r="J24" s="14">
-        <v>1987</v>
+        <v>2301</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.529441368897</v>
+        <v>-4.085180356366</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.451073985680</v>
+        <v>-7.811194653299</v>
       </c>
       <c r="M24" s="15">
-        <v>30.288461538461</v>
+        <v>32.791817087846</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D25" s="14">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E25" s="15">
-        <v>10.869565217391</v>
+        <v>-12.592592592592</v>
       </c>
       <c r="F25" s="14">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="G25" s="14">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="H25" s="15">
-        <v>-20</v>
+        <v>-13.856812933025</v>
       </c>
       <c r="I25" s="14">
-        <v>563</v>
+        <v>685</v>
       </c>
       <c r="J25" s="14">
-        <v>670</v>
+        <v>805</v>
       </c>
       <c r="K25" s="15">
-        <v>-15.970149253731</v>
+        <v>-14.906832298136</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.003250270855</v>
+        <v>-33.040078201368</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="D26" s="14">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E26" s="15">
-        <v>-11.111111111111</v>
+        <v>12.903225806451</v>
       </c>
       <c r="F26" s="14">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="G26" s="14">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="H26" s="15">
-        <v>3.285714285714</v>
+        <v>4.647887323943</v>
       </c>
       <c r="I26" s="14">
-        <v>1208</v>
+        <v>1404</v>
       </c>
       <c r="J26" s="14">
-        <v>1140</v>
+        <v>1326</v>
       </c>
       <c r="K26" s="15">
-        <v>5.964912280701</v>
+        <v>5.882352941176</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.501547987616</v>
+        <v>-5.581708137188</v>
       </c>
       <c r="M26" s="15">
-        <v>5.779334500875</v>
+        <v>7.012195121951</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E27" s="15">
-        <v>-26.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G27" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H27" s="15">
-        <v>12</v>
+        <v>-9.433962264150</v>
       </c>
       <c r="I27" s="14">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="J27" s="14">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K27" s="15">
-        <v>10.256410256410</v>
+        <v>8.791208791208</v>
       </c>
       <c r="L27" s="15">
-        <v>-2.272727272727</v>
+        <v>4.210526315789</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D28" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E28" s="15">
-        <v>25</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F28" s="14">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="G28" s="14">
         <v>61</v>
       </c>
       <c r="H28" s="15">
-        <v>60.655737704918</v>
+        <v>36.065573770491</v>
       </c>
       <c r="I28" s="14">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="J28" s="14">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K28" s="15">
-        <v>29.411764705882</v>
+        <v>26.717557251908</v>
       </c>
       <c r="L28" s="15">
-        <v>28.333333333333</v>
+        <v>21.167883211678</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D29" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E29" s="15">
-        <v>350</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F29" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G29" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H29" s="15">
-        <v>75</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I29" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J29" s="14">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K29" s="15">
-        <v>52</v>
+        <v>31.25</v>
       </c>
       <c r="L29" s="15">
-        <v>-24</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M29" s="15">
-        <v>-22.448979591836</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="N29" s="15">
-        <v>-72.058823529411</v>
+        <v>-73.584905660377</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,63 +1508,63 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D30" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E30" s="15">
-        <v>200</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F30" s="14">
         <v>15</v>
       </c>
       <c r="G30" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H30" s="15">
-        <v>36.363636363636</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J30" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K30" s="15">
-        <v>42.857142857142</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L30" s="15">
-        <v>-16.666666666666</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="M30" s="15">
-        <v>-31.818181818181</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-75.409836065573</v>
+        <v>-76.388888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>2</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>100</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F31" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I31" s="14">
         <v>6</v>
@@ -1576,13 +1576,13 @@
         <v>500</v>
       </c>
       <c r="L31" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" s="14">
         <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J33" s="14">
         <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L33" s="15">
-        <v>-40</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>644</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>17862</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>9538</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>19326</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>8856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>22946</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>79825</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -199,67 +199,67 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
+    <t>Traffic Statistics</t>
+  </si>
+  <si>
+    <t>Traffic Fatalities</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>Traffic Statistics</t>
-  </si>
-  <si>
-    <t>Traffic Fatalities</t>
   </si>
   <si>
     <t>Historical Perspective</t>
@@ -851,743 +851,743 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="14">
         <v>2</v>
       </c>
       <c r="E14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F14" s="14">
         <v>6</v>
       </c>
       <c r="G14" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H14" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K14" s="15">
-        <v>25</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M14" s="15">
-        <v>25</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-79.166666666666</v>
+        <v>-79.487179487179</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D15" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E15" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G15" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H15" s="15">
-        <v>-6.976744186046</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="I15" s="14">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="J15" s="14">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="K15" s="15">
-        <v>19.444444444444</v>
+        <v>17.857142857142</v>
       </c>
       <c r="L15" s="15">
-        <v>40.983606557377</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>115</v>
+        <v>130.232558139535</v>
       </c>
       <c r="N15" s="15">
-        <v>17.808219178082</v>
+        <v>15.116279069767</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
         <v>67</v>
       </c>
       <c r="D16" s="14">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E16" s="15">
-        <v>4.6875</v>
+        <v>-8.219178082191</v>
       </c>
       <c r="F16" s="14">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="G16" s="14">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="H16" s="15">
-        <v>-9.446254071661</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>536</v>
+        <v>604</v>
       </c>
       <c r="J16" s="14">
-        <v>592</v>
+        <v>665</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.459459459459</v>
+        <v>-9.172932330827</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.766570605187</v>
+        <v>-24.215809284818</v>
       </c>
       <c r="M16" s="15">
-        <v>-7.745266781411</v>
+        <v>-4.581358609794</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.478991596638</v>
+        <v>-77.546468401487</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D17" s="14">
-        <v>111</v>
+        <v>169</v>
       </c>
       <c r="E17" s="15">
-        <v>16.216216216216</v>
+        <v>-21.893491124260</v>
       </c>
       <c r="F17" s="14">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="G17" s="14">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="H17" s="15">
-        <v>-0.714285714285</v>
+        <v>-3.315881326352</v>
       </c>
       <c r="I17" s="14">
-        <v>1073</v>
+        <v>1213</v>
       </c>
       <c r="J17" s="14">
-        <v>1058</v>
+        <v>1227</v>
       </c>
       <c r="K17" s="15">
-        <v>1.417769376181</v>
+        <v>-1.140994295028</v>
       </c>
       <c r="L17" s="15">
-        <v>2.876318312559</v>
+        <v>1.421404682274</v>
       </c>
       <c r="M17" s="15">
-        <v>85</v>
+        <v>92.234548335974</v>
       </c>
       <c r="N17" s="15">
-        <v>3.471552555448</v>
+        <v>1.932773109243</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D18" s="14">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E18" s="15">
-        <v>-24.285714285714</v>
+        <v>-32.758620689655</v>
       </c>
       <c r="F18" s="14">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G18" s="14">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H18" s="15">
-        <v>-27.049180327868</v>
+        <v>-23.75</v>
       </c>
       <c r="I18" s="14">
-        <v>358</v>
+        <v>398</v>
       </c>
       <c r="J18" s="14">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="K18" s="15">
-        <v>-18.636363636363</v>
+        <v>-20.080321285140</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.469437652811</v>
+        <v>-15.856236786469</v>
       </c>
       <c r="M18" s="15">
-        <v>-23.010752688172</v>
+        <v>-22.113502935420</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.480362537764</v>
+        <v>-86.715620827770</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="D19" s="14">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E19" s="15">
-        <v>-4.848484848484</v>
+        <v>-30.674846625766</v>
       </c>
       <c r="F19" s="14">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="G19" s="14">
         <v>633</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.060031595576</v>
+        <v>-11.848341232227</v>
       </c>
       <c r="I19" s="14">
-        <v>1057</v>
+        <v>1177</v>
       </c>
       <c r="J19" s="14">
-        <v>1186</v>
+        <v>1349</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.876897133220</v>
+        <v>-12.750185322461</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.166163141994</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M19" s="15">
-        <v>90.794223826714</v>
+        <v>89.533011272141</v>
       </c>
       <c r="N19" s="15">
-        <v>11.733615221987</v>
+        <v>10.933081998115</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D20" s="14">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E20" s="15">
-        <v>-15.714285714285</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="G20" s="14">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="H20" s="15">
-        <v>-15.593220338983</v>
+        <v>-19.377162629757</v>
       </c>
       <c r="I20" s="14">
-        <v>469</v>
+        <v>507</v>
       </c>
       <c r="J20" s="14">
-        <v>558</v>
+        <v>630</v>
       </c>
       <c r="K20" s="15">
-        <v>-15.949820788530</v>
+        <v>-19.523809523809</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.777027027027</v>
+        <v>-23.873873873873</v>
       </c>
       <c r="M20" s="15">
-        <v>73.703703703703</v>
+        <v>66.776315789473</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.081177520071</v>
+        <v>-79.936683814800</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>474</v>
+        <v>403</v>
       </c>
       <c r="D21" s="17">
-        <v>492</v>
+        <v>549</v>
       </c>
       <c r="E21" s="18">
-        <v>-3.658536585365</v>
+        <v>-26.593806921675</v>
       </c>
       <c r="F21" s="17">
-        <v>1851</v>
+        <v>1870</v>
       </c>
       <c r="G21" s="17">
-        <v>2086</v>
+        <v>2079</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.265580057526</v>
+        <v>-10.052910052910</v>
       </c>
       <c r="I21" s="17">
-        <v>3594</v>
+        <v>4014</v>
       </c>
       <c r="J21" s="17">
-        <v>3918</v>
+        <v>4467</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.269525267993</v>
+        <v>-10.141034251175</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.146447559207</v>
+        <v>-14.831317632081</v>
       </c>
       <c r="M21" s="18">
-        <v>43.645083932853</v>
+        <v>45.540246555475</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.757820812938</v>
+        <v>-62.231840421528</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="14">
+        <v>7</v>
+      </c>
+      <c r="D22" s="14">
+        <v>4</v>
+      </c>
+      <c r="E22" s="15">
+        <v>75</v>
+      </c>
+      <c r="F22" s="14">
+        <v>38</v>
+      </c>
+      <c r="G22" s="14">
+        <v>19</v>
+      </c>
+      <c r="H22" s="15">
+        <v>100</v>
+      </c>
+      <c r="I22" s="14">
+        <v>74</v>
+      </c>
+      <c r="J22" s="14">
+        <v>50</v>
+      </c>
+      <c r="K22" s="15">
+        <v>48</v>
+      </c>
+      <c r="L22" s="15">
+        <v>2.777777777777</v>
+      </c>
+      <c r="M22" s="15">
+        <v>89.743589743589</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="C22" s="14">
-        <v>10</v>
-      </c>
-      <c r="D22" s="14">
-        <v>6</v>
-      </c>
-      <c r="E22" s="15">
-        <v>66.666666666666</v>
-      </c>
-      <c r="F22" s="14">
-        <v>40</v>
-      </c>
-      <c r="G22" s="14">
-        <v>25</v>
-      </c>
-      <c r="H22" s="15">
-        <v>60</v>
-      </c>
-      <c r="I22" s="14">
-        <v>67</v>
-      </c>
-      <c r="J22" s="14">
-        <v>46</v>
-      </c>
-      <c r="K22" s="15">
-        <v>45.652173913043</v>
-      </c>
-      <c r="L22" s="15">
-        <v>3.076923076923</v>
-      </c>
-      <c r="M22" s="15">
-        <v>97.058823529411</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D23" s="14">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E23" s="15">
-        <v>-23.529411764705</v>
+        <v>8</v>
       </c>
       <c r="F23" s="14">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G23" s="14">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="H23" s="15">
-        <v>-11.290322580645</v>
+        <v>6.542056074766</v>
       </c>
       <c r="I23" s="14">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="J23" s="14">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="K23" s="15">
-        <v>-4.347826086956</v>
+        <v>-0.431034482758</v>
       </c>
       <c r="L23" s="15">
-        <v>-16.806722689075</v>
+        <v>-16</v>
       </c>
       <c r="M23" s="15">
-        <v>47.761194029850</v>
+        <v>55.033557046979</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>313</v>
+        <v>265</v>
       </c>
       <c r="D24" s="14">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="E24" s="15">
-        <v>-0.318471337579</v>
+        <v>-18.960244648318</v>
       </c>
       <c r="F24" s="14">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="G24" s="14">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.045977011494</v>
+        <v>-7.172300082440</v>
       </c>
       <c r="I24" s="14">
-        <v>2207</v>
+        <v>2480</v>
       </c>
       <c r="J24" s="14">
-        <v>2301</v>
+        <v>2628</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.085180356366</v>
+        <v>-5.631659056316</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.811194653299</v>
+        <v>-9.653916211293</v>
       </c>
       <c r="M24" s="15">
-        <v>32.791817087846</v>
+        <v>35.445111960677</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D25" s="14">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="E25" s="15">
-        <v>-12.592592592592</v>
+        <v>-3.125</v>
       </c>
       <c r="F25" s="14">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="G25" s="14">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="H25" s="15">
-        <v>-13.856812933025</v>
+        <v>-3.676470588235</v>
       </c>
       <c r="I25" s="14">
-        <v>685</v>
+        <v>781</v>
       </c>
       <c r="J25" s="14">
-        <v>805</v>
+        <v>901</v>
       </c>
       <c r="K25" s="15">
-        <v>-14.906832298136</v>
+        <v>-13.318534961154</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.040078201368</v>
+        <v>-31.790393013100</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D26" s="14">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="E26" s="15">
-        <v>12.903225806451</v>
+        <v>10.465116279069</v>
       </c>
       <c r="F26" s="14">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="G26" s="14">
-        <v>710</v>
+        <v>724</v>
       </c>
       <c r="H26" s="15">
-        <v>4.647887323943</v>
+        <v>2.071823204419</v>
       </c>
       <c r="I26" s="14">
-        <v>1404</v>
+        <v>1588</v>
       </c>
       <c r="J26" s="14">
-        <v>1326</v>
+        <v>1498</v>
       </c>
       <c r="K26" s="15">
-        <v>5.882352941176</v>
+        <v>6.008010680907</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.581708137188</v>
+        <v>-6.971294669009</v>
       </c>
       <c r="M26" s="15">
-        <v>7.012195121951</v>
+        <v>6.505700871898</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D27" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="F27" s="14">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G27" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H27" s="15">
-        <v>-9.433962264150</v>
+        <v>-9.836065573770</v>
       </c>
       <c r="I27" s="14">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="J27" s="14">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="K27" s="15">
-        <v>8.791208791208</v>
+        <v>5.454545454545</v>
       </c>
       <c r="L27" s="15">
-        <v>4.210526315789</v>
+        <v>11.538461538461</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D28" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E28" s="15">
-        <v>-7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G28" s="14">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H28" s="15">
-        <v>36.065573770491</v>
+        <v>56.896551724137</v>
       </c>
       <c r="I28" s="14">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="J28" s="14">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="K28" s="15">
-        <v>26.717557251908</v>
+        <v>24.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>21.167883211678</v>
+        <v>20.645161290322</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="14">
         <v>7</v>
       </c>
       <c r="E29" s="15">
-        <v>-42.857142857142</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F29" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H29" s="15">
-        <v>26.666666666666</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I29" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J29" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K29" s="15">
-        <v>31.25</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L29" s="15">
-        <v>-17.647058823529</v>
+        <v>-27.419354838709</v>
       </c>
       <c r="M29" s="15">
-        <v>-26.315789473684</v>
+        <v>-25</v>
       </c>
       <c r="N29" s="15">
-        <v>-73.584905660377</v>
+        <v>-74.576271186440</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="14">
+        <v>3</v>
+      </c>
+      <c r="D30" s="14">
+        <v>6</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F30" s="14">
+        <v>16</v>
+      </c>
+      <c r="G30" s="14">
+        <v>17</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-5.882352941176</v>
+      </c>
+      <c r="I30" s="14">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>4</v>
-      </c>
-      <c r="D30" s="14">
-        <v>7</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-42.857142857142</v>
-      </c>
-      <c r="F30" s="14">
-        <v>15</v>
-      </c>
-      <c r="G30" s="14">
-        <v>15</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
-      </c>
-      <c r="I30" s="14">
+      <c r="J30" s="14">
         <v>34</v>
       </c>
-      <c r="J30" s="14">
-        <v>28</v>
-      </c>
       <c r="K30" s="15">
-        <v>21.428571428571</v>
+        <v>8.823529411764</v>
       </c>
       <c r="L30" s="15">
-        <v>-8.108108108108</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="M30" s="15">
-        <v>-29.166666666666</v>
+        <v>-27.450980392156</v>
       </c>
       <c r="N30" s="15">
-        <v>-76.388888888888</v>
+        <v>-76.582278481012</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>37</v>
+      </c>
+      <c r="C31" s="14">
+        <v>2</v>
+      </c>
+      <c r="D31" s="14">
+        <v>3</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F31" s="14">
         <v>4</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1605,43 +1605,43 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>29</v>
+      <c r="D33" s="14">
+        <v>2</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
+        <v>2</v>
+      </c>
+      <c r="G33" s="14">
         <v>4</v>
       </c>
-      <c r="G33" s="14">
-        <v>2</v>
-      </c>
       <c r="H33" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I33" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J33" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K33" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>-28.571428571428</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>644</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>17862</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>9538</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>19326</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>8856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>22946</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>79825</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -253,13 +253,13 @@
     <t>Hate Crimes</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Traffic Statistics</t>
   </si>
   <si>
     <t>Traffic Fatalities</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Historical Perspective</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -852,40 +852,40 @@
         <v>19</v>
       </c>
       <c r="C14" s="14">
+        <v>2</v>
+      </c>
+      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="14">
-        <v>2</v>
-      </c>
       <c r="E14" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F14" s="14">
         <v>6</v>
       </c>
       <c r="G14" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H14" s="15">
+        <v>20</v>
+      </c>
+      <c r="I14" s="14">
+        <v>18</v>
+      </c>
+      <c r="J14" s="14">
+        <v>15</v>
+      </c>
+      <c r="K14" s="15">
+        <v>20</v>
+      </c>
+      <c r="L14" s="15">
+        <v>-5.263157894736</v>
+      </c>
+      <c r="M14" s="15">
         <v>0</v>
       </c>
-      <c r="I14" s="14">
-        <v>16</v>
-      </c>
-      <c r="J14" s="14">
-        <v>14</v>
-      </c>
-      <c r="K14" s="15">
-        <v>14.285714285714</v>
-      </c>
-      <c r="L14" s="15">
-        <v>-5.882352941176</v>
-      </c>
-      <c r="M14" s="15">
-        <v>6.666666666666</v>
-      </c>
       <c r="N14" s="15">
-        <v>-79.487179487179</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,37 +896,37 @@
         <v>12</v>
       </c>
       <c r="D15" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F15" s="14">
+        <v>40</v>
+      </c>
+      <c r="G15" s="14">
         <v>43</v>
       </c>
-      <c r="G15" s="14">
-        <v>45</v>
-      </c>
       <c r="H15" s="15">
-        <v>-4.444444444444</v>
+        <v>-6.976744186046</v>
       </c>
       <c r="I15" s="14">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="J15" s="14">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K15" s="15">
-        <v>17.857142857142</v>
+        <v>18.085106382978</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>56.338028169014</v>
       </c>
       <c r="M15" s="15">
-        <v>130.232558139535</v>
+        <v>146.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>15.116279069767</v>
+        <v>6.730769230769</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D16" s="14">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E16" s="15">
-        <v>-8.219178082191</v>
+        <v>-10.9375</v>
       </c>
       <c r="F16" s="14">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="G16" s="14">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>0.354609929078</v>
       </c>
       <c r="I16" s="14">
-        <v>604</v>
+        <v>663</v>
       </c>
       <c r="J16" s="14">
-        <v>665</v>
+        <v>729</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.172932330827</v>
+        <v>-9.053497942386</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.215809284818</v>
+        <v>-24.401368301026</v>
       </c>
       <c r="M16" s="15">
-        <v>-4.581358609794</v>
+        <v>-5.014326647564</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.546468401487</v>
+        <v>-77.9</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>132</v>
       </c>
       <c r="D17" s="14">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="E17" s="15">
-        <v>-21.893491124260</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="F17" s="14">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G17" s="14">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.315881326352</v>
+        <v>-1.766784452296</v>
       </c>
       <c r="I17" s="14">
-        <v>1213</v>
+        <v>1352</v>
       </c>
       <c r="J17" s="14">
-        <v>1227</v>
+        <v>1379</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.140994295028</v>
+        <v>-1.957940536620</v>
       </c>
       <c r="L17" s="15">
-        <v>1.421404682274</v>
+        <v>0.670141474311</v>
       </c>
       <c r="M17" s="15">
-        <v>92.234548335974</v>
+        <v>84.699453551912</v>
       </c>
       <c r="N17" s="15">
-        <v>1.932773109243</v>
+        <v>-1.815541031227</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D18" s="14">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E18" s="15">
-        <v>-32.758620689655</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="F18" s="14">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G18" s="14">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="H18" s="15">
-        <v>-23.75</v>
+        <v>-18.942731277533</v>
       </c>
       <c r="I18" s="14">
-        <v>398</v>
+        <v>437</v>
       </c>
       <c r="J18" s="14">
-        <v>498</v>
+        <v>552</v>
       </c>
       <c r="K18" s="15">
-        <v>-20.080321285140</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.856236786469</v>
+        <v>-18.923933209647</v>
       </c>
       <c r="M18" s="15">
-        <v>-22.113502935420</v>
+        <v>-23.198594024604</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.715620827770</v>
+        <v>-86.908328340323</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="D19" s="14">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E19" s="15">
-        <v>-30.674846625766</v>
+        <v>-10.650887573964</v>
       </c>
       <c r="F19" s="14">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="G19" s="14">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.848341232227</v>
+        <v>-9.419152276295</v>
       </c>
       <c r="I19" s="14">
-        <v>1177</v>
+        <v>1334</v>
       </c>
       <c r="J19" s="14">
-        <v>1349</v>
+        <v>1518</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.750185322461</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.428571428571</v>
+        <v>-20.023980815347</v>
       </c>
       <c r="M19" s="15">
-        <v>89.533011272141</v>
+        <v>90.571428571428</v>
       </c>
       <c r="N19" s="15">
-        <v>10.933081998115</v>
+        <v>11.259382819015</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="D20" s="14">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E20" s="15">
-        <v>-45.833333333333</v>
+        <v>5</v>
       </c>
       <c r="F20" s="14">
         <v>233</v>
       </c>
       <c r="G20" s="14">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H20" s="15">
-        <v>-19.377162629757</v>
+        <v>-20.477815699658</v>
       </c>
       <c r="I20" s="14">
-        <v>507</v>
+        <v>593</v>
       </c>
       <c r="J20" s="14">
-        <v>630</v>
+        <v>710</v>
       </c>
       <c r="K20" s="15">
-        <v>-19.523809523809</v>
+        <v>-16.478873239436</v>
       </c>
       <c r="L20" s="15">
-        <v>-23.873873873873</v>
+        <v>-20.188425302826</v>
       </c>
       <c r="M20" s="15">
-        <v>66.776315789473</v>
+        <v>73.900293255132</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.936683814800</v>
+        <v>-79.141751670770</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>403</v>
+        <v>472</v>
       </c>
       <c r="D21" s="17">
-        <v>549</v>
+        <v>530</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.593806921675</v>
+        <v>-10.943396226415</v>
       </c>
       <c r="F21" s="17">
-        <v>1870</v>
+        <v>1879</v>
       </c>
       <c r="G21" s="17">
-        <v>2079</v>
+        <v>2053</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.052910052910</v>
+        <v>-8.475401850949</v>
       </c>
       <c r="I21" s="17">
-        <v>4014</v>
+        <v>4508</v>
       </c>
       <c r="J21" s="17">
-        <v>4467</v>
+        <v>4997</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.141034251175</v>
+        <v>-9.785871522913</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.831317632081</v>
+        <v>-14.296577946768</v>
       </c>
       <c r="M21" s="18">
-        <v>45.540246555475</v>
+        <v>45.278762487914</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.231840421528</v>
+        <v>-62.247717946570</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F22" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G22" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H22" s="15">
+        <v>73.913043478260</v>
+      </c>
+      <c r="I22" s="14">
+        <v>86</v>
+      </c>
+      <c r="J22" s="14">
+        <v>58</v>
+      </c>
+      <c r="K22" s="15">
+        <v>48.275862068965</v>
+      </c>
+      <c r="L22" s="15">
+        <v>7.5</v>
+      </c>
+      <c r="M22" s="15">
         <v>100</v>
-      </c>
-      <c r="I22" s="14">
-        <v>74</v>
-      </c>
-      <c r="J22" s="14">
-        <v>50</v>
-      </c>
-      <c r="K22" s="15">
-        <v>48</v>
-      </c>
-      <c r="L22" s="15">
-        <v>2.777777777777</v>
-      </c>
-      <c r="M22" s="15">
-        <v>89.743589743589</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>28</v>
@@ -1221,37 +1221,37 @@
         <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D23" s="14">
+        <v>17</v>
+      </c>
+      <c r="E23" s="15">
+        <v>105.882352941176</v>
+      </c>
+      <c r="F23" s="14">
+        <v>125</v>
+      </c>
+      <c r="G23" s="14">
+        <v>100</v>
+      </c>
+      <c r="H23" s="15">
         <v>25</v>
       </c>
-      <c r="E23" s="15">
-        <v>8</v>
-      </c>
-      <c r="F23" s="14">
-        <v>114</v>
-      </c>
-      <c r="G23" s="14">
-        <v>107</v>
-      </c>
-      <c r="H23" s="15">
-        <v>6.542056074766</v>
-      </c>
       <c r="I23" s="14">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="J23" s="14">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="K23" s="15">
-        <v>-0.431034482758</v>
+        <v>7.228915662650</v>
       </c>
       <c r="L23" s="15">
-        <v>-16</v>
+        <v>-14.696485623003</v>
       </c>
       <c r="M23" s="15">
-        <v>55.033557046979</v>
+        <v>57.058823529411</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>28</v>
@@ -1262,37 +1262,37 @@
         <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>265</v>
+        <v>347</v>
       </c>
       <c r="D24" s="14">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="E24" s="15">
-        <v>-18.960244648318</v>
+        <v>14.900662251655</v>
       </c>
       <c r="F24" s="14">
-        <v>1126</v>
+        <v>1201</v>
       </c>
       <c r="G24" s="14">
-        <v>1213</v>
+        <v>1245</v>
       </c>
       <c r="H24" s="15">
-        <v>-7.172300082440</v>
+        <v>-3.534136546184</v>
       </c>
       <c r="I24" s="14">
-        <v>2480</v>
+        <v>2830</v>
       </c>
       <c r="J24" s="14">
-        <v>2628</v>
+        <v>2930</v>
       </c>
       <c r="K24" s="15">
-        <v>-5.631659056316</v>
+        <v>-3.412969283276</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.653916211293</v>
+        <v>-7.030223390275</v>
       </c>
       <c r="M24" s="15">
-        <v>35.445111960677</v>
+        <v>38.929798723613</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>28</v>
@@ -1303,34 +1303,34 @@
         <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D25" s="14">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E25" s="15">
-        <v>-3.125</v>
+        <v>1.111111111111</v>
       </c>
       <c r="F25" s="14">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="G25" s="14">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="H25" s="15">
-        <v>-3.676470588235</v>
+        <v>0.968523002421</v>
       </c>
       <c r="I25" s="14">
-        <v>781</v>
+        <v>879</v>
       </c>
       <c r="J25" s="14">
-        <v>901</v>
+        <v>991</v>
       </c>
       <c r="K25" s="15">
-        <v>-13.318534961154</v>
+        <v>-11.301715438950</v>
       </c>
       <c r="L25" s="15">
-        <v>-31.790393013100</v>
+        <v>-29.397590361445</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>28</v>
@@ -1344,37 +1344,37 @@
         <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="D26" s="14">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="E26" s="15">
-        <v>10.465116279069</v>
+        <v>19.786096256684</v>
       </c>
       <c r="F26" s="14">
-        <v>739</v>
+        <v>781</v>
       </c>
       <c r="G26" s="14">
-        <v>724</v>
+        <v>743</v>
       </c>
       <c r="H26" s="15">
-        <v>2.071823204419</v>
+        <v>5.114401076716</v>
       </c>
       <c r="I26" s="14">
-        <v>1588</v>
+        <v>1803</v>
       </c>
       <c r="J26" s="14">
-        <v>1498</v>
+        <v>1685</v>
       </c>
       <c r="K26" s="15">
-        <v>6.008010680907</v>
+        <v>7.002967359050</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.971294669009</v>
+        <v>-5.254860746190</v>
       </c>
       <c r="M26" s="15">
-        <v>6.505700871898</v>
+        <v>5.438596491228</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>28</v>
@@ -1385,34 +1385,34 @@
         <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D27" s="14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E27" s="15">
-        <v>-10.526315789473</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G27" s="14">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H27" s="15">
-        <v>-9.836065573770</v>
+        <v>-12.068965517241</v>
       </c>
       <c r="I27" s="14">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="J27" s="14">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="K27" s="15">
-        <v>5.454545454545</v>
+        <v>5.737704918032</v>
       </c>
       <c r="L27" s="15">
-        <v>11.538461538461</v>
+        <v>16.216216216216</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>28</v>
@@ -1426,34 +1426,34 @@
         <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E28" s="15">
+        <v>-15</v>
+      </c>
+      <c r="F28" s="14">
+        <v>68</v>
+      </c>
+      <c r="G28" s="14">
+        <v>68</v>
+      </c>
+      <c r="H28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="14">
-        <v>91</v>
-      </c>
-      <c r="G28" s="14">
-        <v>58</v>
-      </c>
-      <c r="H28" s="15">
-        <v>56.896551724137</v>
-      </c>
       <c r="I28" s="14">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="J28" s="14">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="K28" s="15">
-        <v>24.666666666666</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L28" s="15">
-        <v>20.645161290322</v>
+        <v>15.606936416185</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>28</v>
@@ -1467,40 +1467,40 @@
         <v>35</v>
       </c>
       <c r="C29" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D29" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>-57.142857142857</v>
+        <v>250</v>
       </c>
       <c r="F29" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G29" s="14">
         <v>18</v>
       </c>
       <c r="H29" s="15">
-        <v>11.111111111111</v>
+        <v>27.777777777777</v>
       </c>
       <c r="I29" s="14">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J29" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K29" s="15">
-        <v>15.384615384615</v>
+        <v>26.829268292682</v>
       </c>
       <c r="L29" s="15">
-        <v>-27.419354838709</v>
+        <v>-22.388059701492</v>
       </c>
       <c r="M29" s="15">
-        <v>-25</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="N29" s="15">
-        <v>-74.576271186440</v>
+        <v>-72.631578947368</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,54 +1508,54 @@
         <v>36</v>
       </c>
       <c r="C30" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D30" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E30" s="15">
-        <v>-50</v>
+        <v>250</v>
       </c>
       <c r="F30" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>17</v>
       </c>
       <c r="H30" s="15">
-        <v>-5.882352941176</v>
+        <v>17.647058823529</v>
       </c>
       <c r="I30" s="14">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J30" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K30" s="15">
-        <v>8.823529411764</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L30" s="15">
-        <v>-21.276595744680</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M30" s="15">
-        <v>-27.450980392156</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="N30" s="15">
-        <v>-76.582278481012</v>
+        <v>-74.269005847953</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="14">
-        <v>2</v>
-      </c>
-      <c r="D31" s="14">
-        <v>3</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-33.333333333333</v>
+      <c r="C31" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F31" s="14">
         <v>4</v>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1605,37 +1605,37 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="14">
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="14">
+        <v>1</v>
+      </c>
+      <c r="G33" s="14">
         <v>2</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F33" s="14">
-        <v>2</v>
-      </c>
-      <c r="G33" s="14">
-        <v>4</v>
       </c>
       <c r="H33" s="15">
         <v>-50</v>
       </c>
       <c r="I33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J33" s="14">
         <v>4</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L33" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>28</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,12 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -223,9 +229,6 @@
     <t>Transit</t>
   </si>
   <si>
-    <t>***.*</t>
-  </si>
-  <si>
     <t>Housing</t>
   </si>
   <si>
@@ -251,9 +254,6 @@
   </si>
   <si>
     <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -852,737 +852,737 @@
         <v>19</v>
       </c>
       <c r="C14" s="14">
-        <v>2</v>
-      </c>
-      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="E14" s="15">
-        <v>100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G14" s="14">
         <v>5</v>
       </c>
       <c r="H14" s="15">
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="I14" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="14">
         <v>15</v>
       </c>
       <c r="K14" s="15">
-        <v>20</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-5.263157894736</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-77.5</v>
+        <v>-79.347826086956</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D15" s="14">
         <v>10</v>
       </c>
       <c r="E15" s="15">
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="F15" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G15" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H15" s="15">
-        <v>-6.976744186046</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="I15" s="14">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="J15" s="14">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="K15" s="15">
-        <v>18.085106382978</v>
+        <v>12.380952380952</v>
       </c>
       <c r="L15" s="15">
-        <v>56.338028169014</v>
+        <v>49.367088607594</v>
       </c>
       <c r="M15" s="15">
-        <v>146.666666666667</v>
+        <v>131.372549019608</v>
       </c>
       <c r="N15" s="15">
-        <v>6.730769230769</v>
+        <v>2.608695652173</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D16" s="14">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E16" s="15">
-        <v>-10.9375</v>
+        <v>-29.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="G16" s="14">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="H16" s="15">
-        <v>0.354609929078</v>
+        <v>-9.782608695652</v>
       </c>
       <c r="I16" s="14">
-        <v>663</v>
+        <v>719</v>
       </c>
       <c r="J16" s="14">
-        <v>729</v>
+        <v>804</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.053497942386</v>
+        <v>-10.572139303482</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.401368301026</v>
+        <v>-24.947807933194</v>
       </c>
       <c r="M16" s="15">
-        <v>-5.014326647564</v>
+        <v>-6.985769728331</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.9</v>
+        <v>-78.005506271030</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D17" s="14">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="E17" s="15">
-        <v>-13.157894736842</v>
+        <v>-21.081081081081</v>
       </c>
       <c r="F17" s="14">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="G17" s="14">
-        <v>566</v>
+        <v>617</v>
       </c>
       <c r="H17" s="15">
-        <v>-1.766784452296</v>
+        <v>-10.210696920583</v>
       </c>
       <c r="I17" s="14">
-        <v>1352</v>
+        <v>1510</v>
       </c>
       <c r="J17" s="14">
-        <v>1379</v>
+        <v>1564</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.957940536620</v>
+        <v>-3.452685421994</v>
       </c>
       <c r="L17" s="15">
-        <v>0.670141474311</v>
+        <v>2.931152010906</v>
       </c>
       <c r="M17" s="15">
-        <v>84.699453551912</v>
+        <v>82.587666263603</v>
       </c>
       <c r="N17" s="15">
-        <v>-1.815541031227</v>
+        <v>0.132625994694</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D18" s="14">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E18" s="15">
-        <v>-37.037037037037</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F18" s="14">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="G18" s="14">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H18" s="15">
-        <v>-18.942731277533</v>
+        <v>-24.675324675324</v>
       </c>
       <c r="I18" s="14">
-        <v>437</v>
+        <v>482</v>
       </c>
       <c r="J18" s="14">
-        <v>552</v>
+        <v>601</v>
       </c>
       <c r="K18" s="15">
-        <v>-20.833333333333</v>
+        <v>-19.800332778702</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.923933209647</v>
+        <v>-18.855218855218</v>
       </c>
       <c r="M18" s="15">
-        <v>-23.198594024604</v>
+        <v>-22.508038585209</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.908328340323</v>
+        <v>-86.765513454146</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D19" s="14">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E19" s="15">
-        <v>-10.650887573964</v>
+        <v>-16.071428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="G19" s="14">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.419152276295</v>
+        <v>-13.984962406015</v>
       </c>
       <c r="I19" s="14">
-        <v>1334</v>
+        <v>1475</v>
       </c>
       <c r="J19" s="14">
-        <v>1518</v>
+        <v>1686</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.121212121212</v>
+        <v>-12.514827995255</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.023980815347</v>
+        <v>-19.442927362097</v>
       </c>
       <c r="M19" s="15">
-        <v>90.571428571428</v>
+        <v>92.307692307692</v>
       </c>
       <c r="N19" s="15">
-        <v>11.259382819015</v>
+        <v>12.167300380228</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D20" s="14">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E20" s="15">
-        <v>5</v>
+        <v>-15.584415584415</v>
       </c>
       <c r="F20" s="14">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="G20" s="14">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="H20" s="15">
-        <v>-20.477815699658</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="I20" s="14">
-        <v>593</v>
+        <v>658</v>
       </c>
       <c r="J20" s="14">
-        <v>710</v>
+        <v>787</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.478873239436</v>
+        <v>-16.391359593392</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.188425302826</v>
+        <v>-18.865598027127</v>
       </c>
       <c r="M20" s="15">
-        <v>73.900293255132</v>
+        <v>75</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.141751670770</v>
+        <v>-78.524804177545</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="D21" s="17">
-        <v>530</v>
+        <v>564</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.943396226415</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="F21" s="17">
-        <v>1879</v>
+        <v>1841</v>
       </c>
       <c r="G21" s="17">
-        <v>2053</v>
+        <v>2135</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.475401850949</v>
+        <v>-13.770491803278</v>
       </c>
       <c r="I21" s="17">
-        <v>4508</v>
+        <v>4981</v>
       </c>
       <c r="J21" s="17">
-        <v>4997</v>
+        <v>5562</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.785871522913</v>
+        <v>-10.445882775979</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.296577946768</v>
+        <v>-13.539316090956</v>
       </c>
       <c r="M21" s="18">
-        <v>45.278762487914</v>
+        <v>45.007278020378</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.247717946570</v>
+        <v>-61.699346405228</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D22" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E22" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G22" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" s="15">
-        <v>73.913043478260</v>
+        <v>41.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J22" s="14">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K22" s="15">
-        <v>48.275862068965</v>
+        <v>42.1875</v>
       </c>
       <c r="L22" s="15">
-        <v>7.5</v>
+        <v>9.638554216867</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>93.617021276595</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E23" s="15">
-        <v>105.882352941176</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F23" s="14">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G23" s="14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H23" s="15">
-        <v>25</v>
+        <v>12.745098039215</v>
       </c>
       <c r="I23" s="14">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="J23" s="14">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="K23" s="15">
-        <v>7.228915662650</v>
+        <v>5.090909090909</v>
       </c>
       <c r="L23" s="15">
-        <v>-14.696485623003</v>
+        <v>-16.473988439306</v>
       </c>
       <c r="M23" s="15">
-        <v>57.058823529411</v>
+        <v>55.376344086021</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="D24" s="14">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="E24" s="15">
-        <v>14.900662251655</v>
+        <v>15.123456790123</v>
       </c>
       <c r="F24" s="14">
-        <v>1201</v>
+        <v>1307</v>
       </c>
       <c r="G24" s="14">
-        <v>1245</v>
+        <v>1267</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.534136546184</v>
+        <v>3.157063930544</v>
       </c>
       <c r="I24" s="14">
-        <v>2830</v>
+        <v>3203</v>
       </c>
       <c r="J24" s="14">
-        <v>2930</v>
+        <v>3254</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.412969283276</v>
+        <v>-1.567301782421</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.030223390275</v>
+        <v>-5.011862396204</v>
       </c>
       <c r="M24" s="15">
-        <v>38.929798723613</v>
+        <v>43.118856121537</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="D25" s="14">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E25" s="15">
-        <v>1.111111111111</v>
+        <v>16.363636363636</v>
       </c>
       <c r="F25" s="14">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="G25" s="14">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="H25" s="15">
-        <v>0.968523002421</v>
+        <v>1.160092807424</v>
       </c>
       <c r="I25" s="14">
-        <v>879</v>
+        <v>1005</v>
       </c>
       <c r="J25" s="14">
-        <v>991</v>
+        <v>1101</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.301715438950</v>
+        <v>-8.719346049046</v>
       </c>
       <c r="L25" s="15">
-        <v>-29.397590361445</v>
+        <v>-25.167535368577</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D26" s="14">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="E26" s="15">
-        <v>19.786096256684</v>
+        <v>4.545454545454</v>
       </c>
       <c r="F26" s="14">
-        <v>781</v>
+        <v>839</v>
       </c>
       <c r="G26" s="14">
-        <v>743</v>
+        <v>765</v>
       </c>
       <c r="H26" s="15">
-        <v>5.114401076716</v>
+        <v>9.673202614379</v>
       </c>
       <c r="I26" s="14">
-        <v>1803</v>
+        <v>2028</v>
       </c>
       <c r="J26" s="14">
-        <v>1685</v>
+        <v>1905</v>
       </c>
       <c r="K26" s="15">
-        <v>7.002967359050</v>
+        <v>6.456692913385</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.254860746190</v>
+        <v>-5.410447761194</v>
       </c>
       <c r="M26" s="15">
-        <v>5.438596491228</v>
+        <v>5.735140771637</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D27" s="14">
         <v>12</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F27" s="14">
         <v>51</v>
       </c>
       <c r="G27" s="14">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H27" s="15">
-        <v>-12.068965517241</v>
+        <v>-7.272727272727</v>
       </c>
       <c r="I27" s="14">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="J27" s="14">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="K27" s="15">
-        <v>5.737704918032</v>
+        <v>3.703703703703</v>
       </c>
       <c r="L27" s="15">
-        <v>16.216216216216</v>
+        <v>12.903225806451</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D28" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E28" s="15">
-        <v>-15</v>
+        <v>16</v>
       </c>
       <c r="F28" s="14">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G28" s="14">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-2.597402597402</v>
       </c>
       <c r="I28" s="14">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="J28" s="14">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="K28" s="15">
-        <v>17.647058823529</v>
+        <v>17.010309278350</v>
       </c>
       <c r="L28" s="15">
-        <v>15.606936416185</v>
+        <v>14.070351758794</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="F29" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G29" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H29" s="15">
-        <v>27.777777777777</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I29" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J29" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K29" s="15">
-        <v>26.829268292682</v>
+        <v>35.714285714285</v>
       </c>
       <c r="L29" s="15">
-        <v>-22.388059701492</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-21.212121212121</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-72.631578947368</v>
+        <v>-72.985781990521</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F30" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G30" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H30" s="15">
-        <v>17.647058823529</v>
+        <v>12.5</v>
       </c>
       <c r="I30" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J30" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K30" s="15">
-        <v>22.222222222222</v>
+        <v>29.729729729729</v>
       </c>
       <c r="L30" s="15">
-        <v>-15.384615384615</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M30" s="15">
-        <v>-21.428571428571</v>
+        <v>-21.311475409836</v>
       </c>
       <c r="N30" s="15">
-        <v>-74.269005847953</v>
+        <v>-74.603174603174</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="13" t="s">
         <v>38</v>
       </c>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
       <c r="D31" s="13" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
         <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L31" s="15">
-        <v>166.666666666667</v>
+        <v>125</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1610,38 +1610,38 @@
       <c r="C33" s="14">
         <v>1</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>28</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>0</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
+        <v>7</v>
+      </c>
+      <c r="J33" s="14">
         <v>5</v>
       </c>
-      <c r="J33" s="14">
-        <v>4</v>
-      </c>
       <c r="K33" s="15">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L33" s="15">
-        <v>-44.444444444444</v>
+        <v>-30</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>644</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>17862</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>9538</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>19326</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>8856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>22946</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>79825</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -851,14 +851,14 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>2</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>4</v>
@@ -873,347 +873,347 @@
         <v>19</v>
       </c>
       <c r="J14" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K14" s="15">
-        <v>26.666666666666</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L14" s="15">
-        <v>-9.523809523809</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-79.347826086956</v>
+        <v>-81.372549019607</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="14">
         <v>10</v>
       </c>
       <c r="E15" s="15">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="F15" s="14">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G15" s="14">
         <v>42</v>
       </c>
       <c r="H15" s="15">
-        <v>-2.380952380952</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="I15" s="14">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="J15" s="14">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="K15" s="15">
-        <v>12.380952380952</v>
+        <v>11.304347826087</v>
       </c>
       <c r="L15" s="15">
-        <v>49.367088607594</v>
+        <v>40.659340659340</v>
       </c>
       <c r="M15" s="15">
-        <v>131.372549019608</v>
+        <v>137.037037037037</v>
       </c>
       <c r="N15" s="15">
-        <v>2.608695652173</v>
+        <v>-1.538461538461</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D16" s="14">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E16" s="15">
-        <v>-29.333333333333</v>
+        <v>-12.345679012345</v>
       </c>
       <c r="F16" s="14">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="G16" s="14">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="H16" s="15">
-        <v>-9.782608695652</v>
+        <v>-11.945392491467</v>
       </c>
       <c r="I16" s="14">
-        <v>719</v>
+        <v>796</v>
       </c>
       <c r="J16" s="14">
-        <v>804</v>
+        <v>885</v>
       </c>
       <c r="K16" s="15">
-        <v>-10.572139303482</v>
+        <v>-10.056497175141</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.947807933194</v>
+        <v>-23.754789272030</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.985769728331</v>
+        <v>-7.656612529002</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.005506271030</v>
+        <v>-77.851975514746</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D17" s="14">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="E17" s="15">
-        <v>-21.081081081081</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="F17" s="14">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="G17" s="14">
-        <v>617</v>
+        <v>668</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.210696920583</v>
+        <v>-12.874251497006</v>
       </c>
       <c r="I17" s="14">
-        <v>1510</v>
+        <v>1672</v>
       </c>
       <c r="J17" s="14">
-        <v>1564</v>
+        <v>1726</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.452685421994</v>
+        <v>-3.128621089223</v>
       </c>
       <c r="L17" s="15">
-        <v>2.931152010906</v>
+        <v>3.915475450590</v>
       </c>
       <c r="M17" s="15">
-        <v>82.587666263603</v>
+        <v>82.732240437158</v>
       </c>
       <c r="N17" s="15">
-        <v>0.132625994694</v>
+        <v>0.420420420420</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D18" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E18" s="15">
-        <v>-14.285714285714</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="F18" s="14">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="G18" s="14">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="H18" s="15">
-        <v>-24.675324675324</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="I18" s="14">
-        <v>482</v>
+        <v>528</v>
       </c>
       <c r="J18" s="14">
-        <v>601</v>
+        <v>655</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.800332778702</v>
+        <v>-19.389312977099</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.855218855218</v>
+        <v>-18.644067796610</v>
       </c>
       <c r="M18" s="15">
-        <v>-22.508038585209</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.765513454146</v>
+        <v>-86.813186813186</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="D19" s="14">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="E19" s="15">
-        <v>-16.071428571428</v>
+        <v>-22.277227722772</v>
       </c>
       <c r="F19" s="14">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="G19" s="14">
-        <v>665</v>
+        <v>702</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.984962406015</v>
+        <v>-18.091168091168</v>
       </c>
       <c r="I19" s="14">
-        <v>1475</v>
+        <v>1643</v>
       </c>
       <c r="J19" s="14">
-        <v>1686</v>
+        <v>1888</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.514827995255</v>
+        <v>-12.976694915254</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.442927362097</v>
+        <v>-18.258706467661</v>
       </c>
       <c r="M19" s="15">
-        <v>92.307692307692</v>
+        <v>92.614302461899</v>
       </c>
       <c r="N19" s="15">
-        <v>12.167300380228</v>
+        <v>14.654570830425</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D20" s="14">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E20" s="15">
-        <v>-15.584415584415</v>
+        <v>-27.380952380952</v>
       </c>
       <c r="F20" s="14">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G20" s="14">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="H20" s="15">
-        <v>-17.391304347826</v>
+        <v>-20.766773162939</v>
       </c>
       <c r="I20" s="14">
-        <v>658</v>
+        <v>716</v>
       </c>
       <c r="J20" s="14">
-        <v>787</v>
+        <v>871</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.391359593392</v>
+        <v>-17.795637198622</v>
       </c>
       <c r="L20" s="15">
-        <v>-18.865598027127</v>
+        <v>-19.004524886877</v>
       </c>
       <c r="M20" s="15">
-        <v>75</v>
+        <v>76.354679802955</v>
       </c>
       <c r="N20" s="15">
-        <v>-78.524804177545</v>
+        <v>-78.537170263789</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="D21" s="17">
-        <v>564</v>
+        <v>595</v>
       </c>
       <c r="E21" s="18">
-        <v>-19.148936170212</v>
+        <v>-17.815126050420</v>
       </c>
       <c r="F21" s="17">
-        <v>1841</v>
+        <v>1872</v>
       </c>
       <c r="G21" s="17">
-        <v>2135</v>
+        <v>2238</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.770491803278</v>
+        <v>-16.353887399463</v>
       </c>
       <c r="I21" s="17">
-        <v>4981</v>
+        <v>5502</v>
       </c>
       <c r="J21" s="17">
-        <v>5562</v>
+        <v>6157</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.445882775979</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.539316090956</v>
+        <v>-12.791250594389</v>
       </c>
       <c r="M21" s="18">
-        <v>45.007278020378</v>
+        <v>45.324881141046</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.699346405228</v>
+        <v>-61.427369601794</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="14">
+        <v>9</v>
+      </c>
+      <c r="D22" s="14">
+        <v>7</v>
+      </c>
+      <c r="E22" s="15">
+        <v>28.571428571428</v>
+      </c>
+      <c r="F22" s="14">
+        <v>33</v>
+      </c>
+      <c r="G22" s="14">
+        <v>25</v>
+      </c>
+      <c r="H22" s="15">
+        <v>32</v>
+      </c>
+      <c r="I22" s="14">
+        <v>100</v>
+      </c>
+      <c r="J22" s="14">
+        <v>71</v>
+      </c>
+      <c r="K22" s="15">
+        <v>40.845070422535</v>
+      </c>
+      <c r="L22" s="15">
+        <v>11.111111111111</v>
+      </c>
+      <c r="M22" s="15">
+        <v>78.571428571428</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C22" s="14">
-        <v>6</v>
-      </c>
-      <c r="D22" s="14">
-        <v>6</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
-      </c>
-      <c r="F22" s="14">
-        <v>34</v>
-      </c>
-      <c r="G22" s="14">
-        <v>24</v>
-      </c>
-      <c r="H22" s="15">
-        <v>41.666666666666</v>
-      </c>
-      <c r="I22" s="14">
-        <v>91</v>
-      </c>
-      <c r="J22" s="14">
-        <v>64</v>
-      </c>
-      <c r="K22" s="15">
-        <v>42.1875</v>
-      </c>
-      <c r="L22" s="15">
-        <v>9.638554216867</v>
-      </c>
-      <c r="M22" s="15">
-        <v>93.617021276595</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D23" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E23" s="15">
-        <v>-23.076923076923</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G23" s="14">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H23" s="15">
-        <v>12.745098039215</v>
+        <v>9.183673469387</v>
       </c>
       <c r="I23" s="14">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="J23" s="14">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="K23" s="15">
-        <v>5.090909090909</v>
+        <v>2.950819672131</v>
       </c>
       <c r="L23" s="15">
-        <v>-16.473988439306</v>
+        <v>-18.441558441558</v>
       </c>
       <c r="M23" s="15">
-        <v>55.376344086021</v>
+        <v>50.961538461538</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>373</v>
+        <v>342</v>
       </c>
       <c r="D24" s="14">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="E24" s="15">
-        <v>15.123456790123</v>
+        <v>-3.661971830985</v>
       </c>
       <c r="F24" s="14">
-        <v>1307</v>
+        <v>1334</v>
       </c>
       <c r="G24" s="14">
-        <v>1267</v>
+        <v>1308</v>
       </c>
       <c r="H24" s="15">
-        <v>3.157063930544</v>
+        <v>1.987767584097</v>
       </c>
       <c r="I24" s="14">
-        <v>3203</v>
+        <v>3546</v>
       </c>
       <c r="J24" s="14">
-        <v>3254</v>
+        <v>3609</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.567301782421</v>
+        <v>-1.745635910224</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.011862396204</v>
+        <v>-4.291497975708</v>
       </c>
       <c r="M24" s="15">
-        <v>43.118856121537</v>
+        <v>44.087769199512</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="D25" s="14">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E25" s="15">
-        <v>16.363636363636</v>
+        <v>-13.445378151260</v>
       </c>
       <c r="F25" s="14">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="G25" s="14">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="H25" s="15">
-        <v>1.160092807424</v>
+        <v>2.650602409638</v>
       </c>
       <c r="I25" s="14">
-        <v>1005</v>
+        <v>1115</v>
       </c>
       <c r="J25" s="14">
-        <v>1101</v>
+        <v>1220</v>
       </c>
       <c r="K25" s="15">
-        <v>-8.719346049046</v>
+        <v>-8.606557377049</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.167535368577</v>
+        <v>-24.560216508795</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="D26" s="14">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="E26" s="15">
-        <v>4.545454545454</v>
+        <v>-15.611814345991</v>
       </c>
       <c r="F26" s="14">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="G26" s="14">
-        <v>765</v>
+        <v>816</v>
       </c>
       <c r="H26" s="15">
-        <v>9.673202614379</v>
+        <v>1.715686274509</v>
       </c>
       <c r="I26" s="14">
-        <v>2028</v>
+        <v>2225</v>
       </c>
       <c r="J26" s="14">
-        <v>1905</v>
+        <v>2142</v>
       </c>
       <c r="K26" s="15">
-        <v>6.456692913385</v>
+        <v>3.874883286647</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.410447761194</v>
+        <v>-5.480033984706</v>
       </c>
       <c r="M26" s="15">
-        <v>5.735140771637</v>
+        <v>3.971962616822</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D27" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E27" s="15">
         <v>-25</v>
       </c>
       <c r="F27" s="14">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G27" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H27" s="15">
-        <v>-7.272727272727</v>
+        <v>-15.254237288135</v>
       </c>
       <c r="I27" s="14">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="J27" s="14">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="K27" s="15">
-        <v>3.703703703703</v>
+        <v>1.986754966887</v>
       </c>
       <c r="L27" s="15">
-        <v>12.903225806451</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,136 +1426,136 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>26</v>
+      </c>
+      <c r="D28" s="14">
+        <v>23</v>
+      </c>
+      <c r="E28" s="15">
+        <v>13.043478260869</v>
+      </c>
+      <c r="F28" s="14">
+        <v>89</v>
+      </c>
+      <c r="G28" s="14">
+        <v>87</v>
+      </c>
+      <c r="H28" s="15">
+        <v>2.298850574712</v>
+      </c>
+      <c r="I28" s="14">
+        <v>253</v>
+      </c>
+      <c r="J28" s="14">
+        <v>217</v>
+      </c>
+      <c r="K28" s="15">
+        <v>16.589861751152</v>
+      </c>
+      <c r="L28" s="15">
+        <v>7.659574468085</v>
+      </c>
+      <c r="M28" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="14">
-        <v>25</v>
-      </c>
-      <c r="E28" s="15">
-        <v>16</v>
-      </c>
-      <c r="F28" s="14">
-        <v>75</v>
-      </c>
-      <c r="G28" s="14">
-        <v>77</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-2.597402597402</v>
-      </c>
-      <c r="I28" s="14">
-        <v>227</v>
-      </c>
-      <c r="J28" s="14">
-        <v>194</v>
-      </c>
-      <c r="K28" s="15">
-        <v>17.010309278350</v>
-      </c>
-      <c r="L28" s="15">
-        <v>14.070351758794</v>
-      </c>
-      <c r="M28" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>5</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" s="15">
-        <v>400</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G29" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H29" s="15">
-        <v>11.764705882352</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I29" s="14">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J29" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K29" s="15">
-        <v>35.714285714285</v>
+        <v>21.739130434782</v>
       </c>
       <c r="L29" s="15">
-        <v>-20.833333333333</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M29" s="15">
-        <v>-20.833333333333</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N29" s="15">
-        <v>-72.985781990521</v>
+        <v>-76.470588235294</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>4</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
       <c r="E30" s="15">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G30" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H30" s="15">
-        <v>12.5</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I30" s="14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J30" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K30" s="15">
-        <v>29.729729729729</v>
+        <v>14.634146341463</v>
       </c>
       <c r="L30" s="15">
-        <v>-15.789473684210</v>
+        <v>-24.193548387096</v>
       </c>
       <c r="M30" s="15">
-        <v>-21.311475409836</v>
+        <v>-36.486486486486</v>
       </c>
       <c r="N30" s="15">
-        <v>-74.603174603174</v>
+        <v>-77.934272300469</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F31" s="14">
         <v>3</v>
@@ -1567,22 +1567,22 @@
         <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>125</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="14">
         <v>1</v>
       </c>
       <c r="E33" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>3</v>
       </c>
       <c r="G33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I33" s="14">
         <v>7</v>
       </c>
       <c r="J33" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L33" s="15">
         <v>-30</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>644</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>17862</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>9538</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>19326</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>8856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>22946</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>79825</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -199,61 +199,61 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -851,720 +851,720 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>2</v>
       </c>
       <c r="D14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F14" s="14">
+        <v>5</v>
+      </c>
+      <c r="G14" s="14">
         <v>4</v>
       </c>
-      <c r="G14" s="14">
-        <v>5</v>
-      </c>
       <c r="H14" s="15">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="I14" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J14" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K14" s="15">
-        <v>11.764705882352</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-13.636363636363</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="M14" s="15">
-        <v>-20.833333333333</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="N14" s="15">
-        <v>-81.372549019607</v>
+        <v>-81.896551724137</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
+        <v>14</v>
+      </c>
+      <c r="D15" s="14">
         <v>9</v>
       </c>
-      <c r="D15" s="14">
-        <v>10</v>
-      </c>
       <c r="E15" s="15">
-        <v>-10</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F15" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G15" s="14">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H15" s="15">
-        <v>-4.761904761904</v>
+        <v>12.820512820512</v>
       </c>
       <c r="I15" s="14">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="J15" s="14">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="K15" s="15">
-        <v>11.304347826087</v>
+        <v>16.129032258064</v>
       </c>
       <c r="L15" s="15">
-        <v>40.659340659340</v>
+        <v>39.805825242718</v>
       </c>
       <c r="M15" s="15">
-        <v>137.037037037037</v>
+        <v>136.065573770492</v>
       </c>
       <c r="N15" s="15">
-        <v>-1.538461538461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" s="14">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E16" s="15">
-        <v>-12.345679012345</v>
+        <v>-6.410256410256</v>
       </c>
       <c r="F16" s="14">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="G16" s="14">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H16" s="15">
-        <v>-11.945392491467</v>
+        <v>-9.731543624161</v>
       </c>
       <c r="I16" s="14">
-        <v>796</v>
+        <v>876</v>
       </c>
       <c r="J16" s="14">
-        <v>885</v>
+        <v>963</v>
       </c>
       <c r="K16" s="15">
-        <v>-10.056497175141</v>
+        <v>-9.034267912772</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.754789272030</v>
+        <v>-22.819383259911</v>
       </c>
       <c r="M16" s="15">
-        <v>-7.656612529002</v>
+        <v>-8.463949843260</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.851975514746</v>
+        <v>-77.675840978593</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="D17" s="14">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E17" s="15">
-        <v>-9.259259259259</v>
+        <v>-10</v>
       </c>
       <c r="F17" s="14">
-        <v>582</v>
+        <v>615</v>
       </c>
       <c r="G17" s="14">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="H17" s="15">
-        <v>-12.874251497006</v>
+        <v>-9.425625920471</v>
       </c>
       <c r="I17" s="14">
-        <v>1672</v>
+        <v>1841</v>
       </c>
       <c r="J17" s="14">
-        <v>1726</v>
+        <v>1906</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.128621089223</v>
+        <v>-3.410283315844</v>
       </c>
       <c r="L17" s="15">
-        <v>3.915475450590</v>
+        <v>4.960091220068</v>
       </c>
       <c r="M17" s="15">
-        <v>82.732240437158</v>
+        <v>86.903553299492</v>
       </c>
       <c r="N17" s="15">
-        <v>0.420420420420</v>
+        <v>1.265126512651</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D18" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E18" s="15">
-        <v>-18.518518518518</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G18" s="14">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H18" s="15">
-        <v>-23.255813953488</v>
+        <v>-23.502304147465</v>
       </c>
       <c r="I18" s="14">
-        <v>528</v>
+        <v>574</v>
       </c>
       <c r="J18" s="14">
-        <v>655</v>
+        <v>715</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.389312977099</v>
+        <v>-19.720279720279</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.644067796610</v>
+        <v>-18.811881188118</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.428571428571</v>
+        <v>-22.327469553450</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.813186813186</v>
+        <v>-86.849942726231</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D19" s="14">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.277227722772</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>575</v>
+        <v>626</v>
       </c>
       <c r="G19" s="14">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.091168091168</v>
+        <v>-11.456859971711</v>
       </c>
       <c r="I19" s="14">
-        <v>1643</v>
+        <v>1819</v>
       </c>
       <c r="J19" s="14">
-        <v>1888</v>
+        <v>2056</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.976694915254</v>
+        <v>-11.527237354085</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.258706467661</v>
+        <v>-17.318181818181</v>
       </c>
       <c r="M19" s="15">
-        <v>92.614302461899</v>
+        <v>98.580786026200</v>
       </c>
       <c r="N19" s="15">
-        <v>14.654570830425</v>
+        <v>16.155810983397</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D20" s="14">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="E20" s="15">
-        <v>-27.380952380952</v>
+        <v>-22.772277227722</v>
       </c>
       <c r="F20" s="14">
-        <v>248</v>
+        <v>285</v>
       </c>
       <c r="G20" s="14">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="H20" s="15">
-        <v>-20.766773162939</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>716</v>
+        <v>792</v>
       </c>
       <c r="J20" s="14">
-        <v>871</v>
+        <v>972</v>
       </c>
       <c r="K20" s="15">
-        <v>-17.795637198622</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="L20" s="15">
-        <v>-19.004524886877</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M20" s="15">
-        <v>76.354679802955</v>
+        <v>76.391982182628</v>
       </c>
       <c r="N20" s="15">
-        <v>-78.537170263789</v>
+        <v>-78.253706754530</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>489</v>
+        <v>537</v>
       </c>
       <c r="D21" s="17">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.815126050420</v>
+        <v>-10.050251256281</v>
       </c>
       <c r="F21" s="17">
-        <v>1872</v>
+        <v>2010</v>
       </c>
       <c r="G21" s="17">
-        <v>2238</v>
+        <v>2286</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.353887399463</v>
+        <v>-12.073490813648</v>
       </c>
       <c r="I21" s="17">
-        <v>5502</v>
+        <v>6067</v>
       </c>
       <c r="J21" s="17">
-        <v>6157</v>
+        <v>6754</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.638297872340</v>
+        <v>-10.171750074030</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.791250594389</v>
+        <v>-11.533974919801</v>
       </c>
       <c r="M21" s="18">
-        <v>45.324881141046</v>
+        <v>46.687620889748</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.427369601794</v>
+        <v>-61.046548956661</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="14">
+        <v>3</v>
+      </c>
+      <c r="D22" s="14">
+        <v>6</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F22" s="14">
+        <v>30</v>
+      </c>
+      <c r="G22" s="14">
+        <v>27</v>
+      </c>
+      <c r="H22" s="15">
+        <v>11.111111111111</v>
+      </c>
+      <c r="I22" s="14">
+        <v>103</v>
+      </c>
+      <c r="J22" s="14">
+        <v>77</v>
+      </c>
+      <c r="K22" s="15">
+        <v>33.766233766233</v>
+      </c>
+      <c r="L22" s="15">
+        <v>7.291666666666</v>
+      </c>
+      <c r="M22" s="15">
+        <v>71.666666666666</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="C22" s="14">
-        <v>9</v>
-      </c>
-      <c r="D22" s="14">
-        <v>7</v>
-      </c>
-      <c r="E22" s="15">
-        <v>28.571428571428</v>
-      </c>
-      <c r="F22" s="14">
-        <v>33</v>
-      </c>
-      <c r="G22" s="14">
-        <v>25</v>
-      </c>
-      <c r="H22" s="15">
-        <v>32</v>
-      </c>
-      <c r="I22" s="14">
-        <v>100</v>
-      </c>
-      <c r="J22" s="14">
-        <v>71</v>
-      </c>
-      <c r="K22" s="15">
-        <v>40.845070422535</v>
-      </c>
-      <c r="L22" s="15">
-        <v>11.111111111111</v>
-      </c>
-      <c r="M22" s="15">
-        <v>78.571428571428</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D23" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" s="15">
-        <v>-26.666666666666</v>
+        <v>16.129032258064</v>
       </c>
       <c r="F23" s="14">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="G23" s="14">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H23" s="15">
-        <v>9.183673469387</v>
+        <v>13.461538461538</v>
       </c>
       <c r="I23" s="14">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="J23" s="14">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="K23" s="15">
-        <v>2.950819672131</v>
+        <v>5.059523809523</v>
       </c>
       <c r="L23" s="15">
-        <v>-18.441558441558</v>
+        <v>-14.939759036144</v>
       </c>
       <c r="M23" s="15">
-        <v>50.961538461538</v>
+        <v>54.824561403508</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>342</v>
+        <v>433</v>
       </c>
       <c r="D24" s="14">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.661971830985</v>
+        <v>12.467532467532</v>
       </c>
       <c r="F24" s="14">
-        <v>1334</v>
+        <v>1488</v>
       </c>
       <c r="G24" s="14">
-        <v>1308</v>
+        <v>1366</v>
       </c>
       <c r="H24" s="15">
-        <v>1.987767584097</v>
+        <v>8.931185944363</v>
       </c>
       <c r="I24" s="14">
-        <v>3546</v>
+        <v>3967</v>
       </c>
       <c r="J24" s="14">
-        <v>3609</v>
+        <v>3994</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.745635910224</v>
+        <v>-0.676014021031</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.291497975708</v>
+        <v>-2.097729516288</v>
       </c>
       <c r="M24" s="15">
-        <v>44.087769199512</v>
+        <v>45.738427626745</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>103</v>
+        <v>158</v>
       </c>
       <c r="D25" s="14">
         <v>119</v>
       </c>
       <c r="E25" s="15">
-        <v>-13.445378151260</v>
+        <v>32.773109243697</v>
       </c>
       <c r="F25" s="14">
-        <v>426</v>
+        <v>493</v>
       </c>
       <c r="G25" s="14">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="H25" s="15">
-        <v>2.650602409638</v>
+        <v>12.557077625570</v>
       </c>
       <c r="I25" s="14">
-        <v>1115</v>
+        <v>1278</v>
       </c>
       <c r="J25" s="14">
-        <v>1220</v>
+        <v>1339</v>
       </c>
       <c r="K25" s="15">
-        <v>-8.606557377049</v>
+        <v>-4.555638536221</v>
       </c>
       <c r="L25" s="15">
-        <v>-24.560216508795</v>
+        <v>-22.73276904474</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="D26" s="14">
-        <v>237</v>
+        <v>189</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.611814345991</v>
+        <v>25.925925925925</v>
       </c>
       <c r="F26" s="14">
-        <v>830</v>
+        <v>882</v>
       </c>
       <c r="G26" s="14">
-        <v>816</v>
+        <v>833</v>
       </c>
       <c r="H26" s="15">
-        <v>1.715686274509</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I26" s="14">
-        <v>2225</v>
+        <v>2460</v>
       </c>
       <c r="J26" s="14">
-        <v>2142</v>
+        <v>2331</v>
       </c>
       <c r="K26" s="15">
-        <v>3.874883286647</v>
+        <v>5.534105534105</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.480033984706</v>
+        <v>-2.497027348394</v>
       </c>
       <c r="M26" s="15">
-        <v>3.971962616822</v>
+        <v>4.502973661852</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E27" s="15">
-        <v>-25</v>
+        <v>36.363636363636</v>
       </c>
       <c r="F27" s="14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G27" s="14">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H27" s="15">
-        <v>-15.254237288135</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="I27" s="14">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="J27" s="14">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="K27" s="15">
-        <v>1.986754966887</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L27" s="15">
-        <v>7.692307692307</v>
+        <v>6.211180124223</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D28" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E28" s="15">
-        <v>13.043478260869</v>
+        <v>21.052631578947</v>
       </c>
       <c r="F28" s="14">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G28" s="14">
         <v>87</v>
       </c>
       <c r="H28" s="15">
-        <v>2.298850574712</v>
+        <v>6.896551724137</v>
       </c>
       <c r="I28" s="14">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="J28" s="14">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="K28" s="15">
-        <v>16.589861751152</v>
+        <v>16.101694915254</v>
       </c>
       <c r="L28" s="15">
-        <v>7.659574468085</v>
+        <v>8.300395256917</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+        <v>35</v>
+      </c>
+      <c r="C29" s="14">
+        <v>5</v>
       </c>
       <c r="D29" s="14">
         <v>4</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>25</v>
       </c>
       <c r="F29" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G29" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H29" s="15">
-        <v>7.142857142857</v>
+        <v>54.545454545454</v>
       </c>
       <c r="I29" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J29" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K29" s="15">
-        <v>21.739130434782</v>
+        <v>22</v>
       </c>
       <c r="L29" s="15">
-        <v>-27.272727272727</v>
+        <v>-26.506024096385</v>
       </c>
       <c r="M29" s="15">
-        <v>-36.363636363636</v>
+        <v>-35.106382978723</v>
       </c>
       <c r="N29" s="15">
-        <v>-76.470588235294</v>
+        <v>-76.806083650190</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="C30" s="14">
+        <v>4</v>
       </c>
       <c r="D30" s="14">
         <v>4</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G30" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H30" s="15">
-        <v>7.692307692307</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I30" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J30" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K30" s="15">
-        <v>14.634146341463</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-24.193548387096</v>
+        <v>-23.880597014925</v>
       </c>
       <c r="M30" s="15">
-        <v>-36.486486486486</v>
+        <v>-36.25</v>
       </c>
       <c r="N30" s="15">
-        <v>-77.934272300469</v>
+        <v>-78.481012658227</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="D31" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
-      </c>
-      <c r="G31" s="14">
-        <v>3</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="I31" s="14">
         <v>8</v>
@@ -1579,10 +1579,10 @@
         <v>33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,7 +1608,7 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D33" s="14">
         <v>1</v>
@@ -1620,28 +1620,28 @@
         <v>3</v>
       </c>
       <c r="G33" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H33" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <v>7</v>
       </c>
       <c r="J33" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K33" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
         <v>-30</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>644</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>17862</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>9538</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>19326</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>8856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>22946</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>79825</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -855,37 +855,37 @@
         <v>2</v>
       </c>
       <c r="D14" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H14" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
+        <v>24</v>
+      </c>
+      <c r="J14" s="14">
         <v>21</v>
       </c>
-      <c r="J14" s="14">
-        <v>18</v>
-      </c>
       <c r="K14" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L14" s="15">
-        <v>-8.695652173913</v>
+        <v>-4</v>
       </c>
       <c r="M14" s="15">
-        <v>-27.586206896551</v>
+        <v>-20</v>
       </c>
       <c r="N14" s="15">
-        <v>-81.896551724137</v>
+        <v>-80.952380952380</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D15" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E15" s="15">
-        <v>55.555555555555</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="14">
+        <v>41</v>
+      </c>
+      <c r="G15" s="14">
         <v>44</v>
       </c>
-      <c r="G15" s="14">
-        <v>39</v>
-      </c>
       <c r="H15" s="15">
-        <v>12.820512820512</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="I15" s="14">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="J15" s="14">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="K15" s="15">
-        <v>16.129032258064</v>
+        <v>11.510791366906</v>
       </c>
       <c r="L15" s="15">
-        <v>39.805825242718</v>
+        <v>35.964912280701</v>
       </c>
       <c r="M15" s="15">
-        <v>136.065573770492</v>
+        <v>124.63768115942</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-3.125</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D16" s="14">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E16" s="15">
-        <v>-6.410256410256</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="G16" s="14">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="H16" s="15">
-        <v>-9.731543624161</v>
+        <v>-9.235668789808</v>
       </c>
       <c r="I16" s="14">
-        <v>876</v>
+        <v>958</v>
       </c>
       <c r="J16" s="14">
-        <v>963</v>
+        <v>1043</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.034267912772</v>
+        <v>-8.149568552253</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.819383259911</v>
+        <v>-22.113821138211</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.463949843260</v>
+        <v>-6.170421155729</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.675840978593</v>
+        <v>-77.314705185886</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="D17" s="14">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="E17" s="15">
-        <v>-10</v>
+        <v>9.638554216867</v>
       </c>
       <c r="F17" s="14">
-        <v>615</v>
+        <v>666</v>
       </c>
       <c r="G17" s="14">
-        <v>679</v>
+        <v>693</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.425625920471</v>
+        <v>-3.896103896103</v>
       </c>
       <c r="I17" s="14">
-        <v>1841</v>
+        <v>2040</v>
       </c>
       <c r="J17" s="14">
-        <v>1906</v>
+        <v>2072</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.410283315844</v>
+        <v>-1.544401544401</v>
       </c>
       <c r="L17" s="15">
-        <v>4.960091220068</v>
+        <v>7.708553326293</v>
       </c>
       <c r="M17" s="15">
-        <v>86.903553299492</v>
+        <v>92.634560906515</v>
       </c>
       <c r="N17" s="15">
-        <v>1.265126512651</v>
+        <v>2.409638554216</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D18" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F18" s="14">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G18" s="14">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="H18" s="15">
-        <v>-23.502304147465</v>
+        <v>-26.106194690265</v>
       </c>
       <c r="I18" s="14">
-        <v>574</v>
+        <v>611</v>
       </c>
       <c r="J18" s="14">
-        <v>715</v>
+        <v>778</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.720279720279</v>
+        <v>-21.465295629820</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.811881188118</v>
+        <v>-18.641810918775</v>
       </c>
       <c r="M18" s="15">
-        <v>-22.327469553450</v>
+        <v>-21.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.849942726231</v>
+        <v>-87.117857895846</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="D19" s="14">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-2.054794520547</v>
       </c>
       <c r="F19" s="14">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="G19" s="14">
-        <v>707</v>
+        <v>684</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.456859971711</v>
+        <v>-10.672514619883</v>
       </c>
       <c r="I19" s="14">
-        <v>1819</v>
+        <v>1963</v>
       </c>
       <c r="J19" s="14">
-        <v>2056</v>
+        <v>2202</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.527237354085</v>
+        <v>-10.853769300635</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.318181818181</v>
+        <v>-16.927634363097</v>
       </c>
       <c r="M19" s="15">
-        <v>98.580786026200</v>
+        <v>98.483316481294</v>
       </c>
       <c r="N19" s="15">
-        <v>16.155810983397</v>
+        <v>14.728229105786</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D20" s="14">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="E20" s="15">
-        <v>-22.772277227722</v>
+        <v>-25.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="G20" s="14">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="H20" s="15">
-        <v>-16.666666666666</v>
+        <v>-23.145400593471</v>
       </c>
       <c r="I20" s="14">
-        <v>792</v>
+        <v>849</v>
       </c>
       <c r="J20" s="14">
-        <v>972</v>
+        <v>1047</v>
       </c>
       <c r="K20" s="15">
-        <v>-18.518518518518</v>
+        <v>-18.911174785100</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.384615384615</v>
+        <v>-15.353938185443</v>
       </c>
       <c r="M20" s="15">
-        <v>76.391982182628</v>
+        <v>73.975409836065</v>
       </c>
       <c r="N20" s="15">
-        <v>-78.253706754530</v>
+        <v>-78.555190704723</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>537</v>
+        <v>509</v>
       </c>
       <c r="D21" s="17">
-        <v>597</v>
+        <v>548</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.050251256281</v>
+        <v>-7.116788321167</v>
       </c>
       <c r="F21" s="17">
-        <v>2010</v>
+        <v>2035</v>
       </c>
       <c r="G21" s="17">
-        <v>2286</v>
+        <v>2304</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.073490813648</v>
+        <v>-11.675347222222</v>
       </c>
       <c r="I21" s="17">
-        <v>6067</v>
+        <v>6600</v>
       </c>
       <c r="J21" s="17">
-        <v>6754</v>
+        <v>7302</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.171750074030</v>
+        <v>-9.613804437140</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.533974919801</v>
+        <v>-10.569105691056</v>
       </c>
       <c r="M21" s="18">
-        <v>46.687620889748</v>
+        <v>48.782687105500</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.046548956661</v>
+        <v>-60.979070592408</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>150</v>
       </c>
       <c r="F22" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G22" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H22" s="15">
-        <v>11.111111111111</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I22" s="14">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J22" s="14">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K22" s="15">
-        <v>33.766233766233</v>
+        <v>37.974683544303</v>
       </c>
       <c r="L22" s="15">
-        <v>7.291666666666</v>
+        <v>4.807692307692</v>
       </c>
       <c r="M22" s="15">
-        <v>71.666666666666</v>
+        <v>70.3125</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>28</v>
@@ -1221,37 +1221,37 @@
         <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D23" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E23" s="15">
-        <v>16.129032258064</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="F23" s="14">
         <v>118</v>
       </c>
       <c r="G23" s="14">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="H23" s="15">
-        <v>13.461538461538</v>
+        <v>-6.349206349206</v>
       </c>
       <c r="I23" s="14">
-        <v>353</v>
+        <v>398</v>
       </c>
       <c r="J23" s="14">
-        <v>336</v>
+        <v>375</v>
       </c>
       <c r="K23" s="15">
-        <v>5.059523809523</v>
+        <v>6.133333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-14.939759036144</v>
+        <v>-9.132420091324</v>
       </c>
       <c r="M23" s="15">
-        <v>54.824561403508</v>
+        <v>65.145228215767</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>28</v>
@@ -1262,37 +1262,37 @@
         <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>433</v>
+        <v>296</v>
       </c>
       <c r="D24" s="14">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E24" s="15">
-        <v>12.467532467532</v>
+        <v>-22.105263157894</v>
       </c>
       <c r="F24" s="14">
-        <v>1488</v>
+        <v>1438</v>
       </c>
       <c r="G24" s="14">
-        <v>1366</v>
+        <v>1444</v>
       </c>
       <c r="H24" s="15">
-        <v>8.931185944363</v>
+        <v>-0.415512465373</v>
       </c>
       <c r="I24" s="14">
-        <v>3967</v>
+        <v>4259</v>
       </c>
       <c r="J24" s="14">
-        <v>3994</v>
+        <v>4374</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.676014021031</v>
+        <v>-2.629172382258</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.097729516288</v>
+        <v>-2.136948529411</v>
       </c>
       <c r="M24" s="15">
-        <v>45.738427626745</v>
+        <v>44.667119565217</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>28</v>
@@ -1303,34 +1303,34 @@
         <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="D25" s="14">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E25" s="15">
-        <v>32.773109243697</v>
+        <v>-28.813559322033</v>
       </c>
       <c r="F25" s="14">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="G25" s="14">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="H25" s="15">
-        <v>12.557077625570</v>
+        <v>5.150214592274</v>
       </c>
       <c r="I25" s="14">
-        <v>1278</v>
+        <v>1365</v>
       </c>
       <c r="J25" s="14">
-        <v>1339</v>
+        <v>1457</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.555638536221</v>
+        <v>-6.314344543582</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.73276904474</v>
+        <v>-22.968397291196</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>28</v>
@@ -1344,37 +1344,37 @@
         <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D26" s="14">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="E26" s="15">
-        <v>25.925925925925</v>
+        <v>1.652892561983</v>
       </c>
       <c r="F26" s="14">
-        <v>882</v>
+        <v>905</v>
       </c>
       <c r="G26" s="14">
-        <v>833</v>
+        <v>888</v>
       </c>
       <c r="H26" s="15">
-        <v>5.882352941176</v>
+        <v>1.914414414414</v>
       </c>
       <c r="I26" s="14">
-        <v>2460</v>
+        <v>2696</v>
       </c>
       <c r="J26" s="14">
-        <v>2331</v>
+        <v>2573</v>
       </c>
       <c r="K26" s="15">
-        <v>5.534105534105</v>
+        <v>4.780411970462</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.497027348394</v>
+        <v>0.935979034069</v>
       </c>
       <c r="M26" s="15">
-        <v>4.502973661852</v>
+        <v>6.519162386408</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>28</v>
@@ -1385,34 +1385,34 @@
         <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D27" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E27" s="15">
-        <v>36.363636363636</v>
+        <v>-31.25</v>
       </c>
       <c r="F27" s="14">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G27" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H27" s="15">
-        <v>-3.921568627450</v>
+        <v>-14.545454545454</v>
       </c>
       <c r="I27" s="14">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="J27" s="14">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="K27" s="15">
-        <v>5.555555555555</v>
+        <v>2.808988764044</v>
       </c>
       <c r="L27" s="15">
-        <v>6.211180124223</v>
+        <v>3.389830508474</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>28</v>
@@ -1426,34 +1426,34 @@
         <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E28" s="15">
-        <v>21.052631578947</v>
+        <v>-40</v>
       </c>
       <c r="F28" s="14">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G28" s="14">
         <v>87</v>
       </c>
       <c r="H28" s="15">
-        <v>6.896551724137</v>
+        <v>1.149425287356</v>
       </c>
       <c r="I28" s="14">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="J28" s="14">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="K28" s="15">
-        <v>16.101694915254</v>
+        <v>10.9375</v>
       </c>
       <c r="L28" s="15">
-        <v>8.300395256917</v>
+        <v>0.709219858156</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>28</v>
@@ -1467,40 +1467,40 @@
         <v>35</v>
       </c>
       <c r="C29" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D29" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E29" s="15">
-        <v>25</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F29" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H29" s="15">
-        <v>54.545454545454</v>
+        <v>12.5</v>
       </c>
       <c r="I29" s="14">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J29" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K29" s="15">
-        <v>22</v>
+        <v>22.807017543859</v>
       </c>
       <c r="L29" s="15">
-        <v>-26.506024096385</v>
+        <v>-19.540229885057</v>
       </c>
       <c r="M29" s="15">
-        <v>-35.106382978723</v>
+        <v>-32.692307692307</v>
       </c>
       <c r="N29" s="15">
-        <v>-76.806083650190</v>
+        <v>-75.609756097561</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,48 +1508,48 @@
         <v>36</v>
       </c>
       <c r="C30" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D30" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F30" s="14">
         <v>15</v>
       </c>
       <c r="G30" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H30" s="15">
-        <v>36.363636363636</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
+        <v>58</v>
+      </c>
+      <c r="J30" s="14">
         <v>51</v>
       </c>
-      <c r="J30" s="14">
-        <v>45</v>
-      </c>
       <c r="K30" s="15">
-        <v>13.333333333333</v>
+        <v>13.725490196078</v>
       </c>
       <c r="L30" s="15">
-        <v>-23.880597014925</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="M30" s="15">
-        <v>-36.25</v>
+        <v>-35.555555555555</v>
       </c>
       <c r="N30" s="15">
-        <v>-78.481012658227</v>
+        <v>-77.519379844961</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>38</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>38</v>
@@ -1558,7 +1558,7 @@
         <v>28</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>38</v>
@@ -1567,16 +1567,16 @@
         <v>28</v>
       </c>
       <c r="I31" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="L31" s="15">
-        <v>33.333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>28</v>
@@ -1607,35 +1607,35 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>38</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="14">
         <v>1</v>
       </c>
       <c r="E33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F33" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I33" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J33" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K33" s="15">
         <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>28</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,9 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -251,9 +254,6 @@
   </si>
   <si>
     <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,738 +851,738 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>2</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I14" s="14">
         <v>24</v>
       </c>
       <c r="J14" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K14" s="15">
-        <v>14.285714285714</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L14" s="15">
         <v>-4</v>
       </c>
       <c r="M14" s="15">
-        <v>-20</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="N14" s="15">
-        <v>-80.952380952380</v>
+        <v>-82.481751824817</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
+        <v>11</v>
+      </c>
+      <c r="D15" s="14">
+        <v>6</v>
+      </c>
+      <c r="E15" s="15">
+        <v>83.333333333333</v>
+      </c>
+      <c r="F15" s="14">
+        <v>44</v>
+      </c>
+      <c r="G15" s="14">
+        <v>40</v>
+      </c>
+      <c r="H15" s="15">
         <v>10</v>
       </c>
-      <c r="D15" s="14">
-        <v>15</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F15" s="14">
-        <v>41</v>
-      </c>
-      <c r="G15" s="14">
-        <v>44</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-6.818181818181</v>
-      </c>
       <c r="I15" s="14">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="J15" s="14">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K15" s="15">
-        <v>11.510791366906</v>
+        <v>13.793103448275</v>
       </c>
       <c r="L15" s="15">
-        <v>35.964912280701</v>
+        <v>38.655462184873</v>
       </c>
       <c r="M15" s="15">
-        <v>124.63768115942</v>
+        <v>117.105263157895</v>
       </c>
       <c r="N15" s="15">
-        <v>-3.125</v>
+        <v>-5.172413793103</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D16" s="14">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-23.655913978494</v>
       </c>
       <c r="F16" s="14">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="G16" s="14">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="H16" s="15">
-        <v>-9.235668789808</v>
+        <v>-9.036144578313</v>
       </c>
       <c r="I16" s="14">
-        <v>958</v>
+        <v>1032</v>
       </c>
       <c r="J16" s="14">
-        <v>1043</v>
+        <v>1136</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.149568552253</v>
+        <v>-9.154929577464</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.113821138211</v>
+        <v>-21.580547112462</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.170421155729</v>
+        <v>-4.884792626728</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.314705185886</v>
+        <v>-77.193370165745</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="D17" s="14">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="E17" s="15">
-        <v>9.638554216867</v>
+        <v>-5.298013245033</v>
       </c>
       <c r="F17" s="14">
-        <v>666</v>
+        <v>647</v>
       </c>
       <c r="G17" s="14">
-        <v>693</v>
+        <v>659</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.896103896103</v>
+        <v>-1.820940819423</v>
       </c>
       <c r="I17" s="14">
-        <v>2040</v>
+        <v>2186</v>
       </c>
       <c r="J17" s="14">
-        <v>2072</v>
+        <v>2223</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.544401544401</v>
+        <v>-1.664417453891</v>
       </c>
       <c r="L17" s="15">
-        <v>7.708553326293</v>
+        <v>6.894865525672</v>
       </c>
       <c r="M17" s="15">
-        <v>92.634560906515</v>
+        <v>90.584132519616</v>
       </c>
       <c r="N17" s="15">
-        <v>2.409638554216</v>
+        <v>1.721731037691</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D18" s="14">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E18" s="15">
-        <v>-42.857142857142</v>
+        <v>-15.517241379310</v>
       </c>
       <c r="F18" s="14">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G18" s="14">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="H18" s="15">
-        <v>-26.106194690265</v>
+        <v>-25.106382978723</v>
       </c>
       <c r="I18" s="14">
-        <v>611</v>
+        <v>661</v>
       </c>
       <c r="J18" s="14">
-        <v>778</v>
+        <v>836</v>
       </c>
       <c r="K18" s="15">
-        <v>-21.465295629820</v>
+        <v>-20.933014354067</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.641810918775</v>
+        <v>-17.786069651741</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.666666666666</v>
+        <v>-21.496437054631</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.117857895846</v>
+        <v>-87.008647798742</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D19" s="14">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="E19" s="15">
-        <v>-2.054794520547</v>
+        <v>-15.697674418604</v>
       </c>
       <c r="F19" s="14">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="G19" s="14">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="H19" s="15">
-        <v>-10.672514619883</v>
+        <v>-10.755813953488</v>
       </c>
       <c r="I19" s="14">
-        <v>1963</v>
+        <v>2110</v>
       </c>
       <c r="J19" s="14">
-        <v>2202</v>
+        <v>2374</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.853769300635</v>
+        <v>-11.120471777590</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.927634363097</v>
+        <v>-15.6</v>
       </c>
       <c r="M19" s="15">
-        <v>98.483316481294</v>
+        <v>96.279069767441</v>
       </c>
       <c r="N19" s="15">
-        <v>14.728229105786</v>
+        <v>14.425162689804</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="14">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="E20" s="15">
-        <v>-25.333333333333</v>
+        <v>-39.361702127659</v>
       </c>
       <c r="F20" s="14">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="G20" s="14">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="H20" s="15">
-        <v>-23.145400593471</v>
+        <v>-29.096045197740</v>
       </c>
       <c r="I20" s="14">
-        <v>849</v>
+        <v>902</v>
       </c>
       <c r="J20" s="14">
-        <v>1047</v>
+        <v>1141</v>
       </c>
       <c r="K20" s="15">
-        <v>-18.911174785100</v>
+        <v>-20.946538124452</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.353938185443</v>
+        <v>-16.712834718374</v>
       </c>
       <c r="M20" s="15">
-        <v>73.975409836065</v>
+        <v>75.486381322957</v>
       </c>
       <c r="N20" s="15">
-        <v>-78.555190704723</v>
+        <v>-78.811369509043</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="D21" s="17">
-        <v>548</v>
+        <v>575</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.116788321167</v>
+        <v>-17.217391304347</v>
       </c>
       <c r="F21" s="17">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="G21" s="17">
-        <v>2304</v>
+        <v>2315</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.675347222222</v>
+        <v>-11.922246220302</v>
       </c>
       <c r="I21" s="17">
-        <v>6600</v>
+        <v>7080</v>
       </c>
       <c r="J21" s="17">
-        <v>7302</v>
+        <v>7877</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.613804437140</v>
+        <v>-10.118065253269</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.569105691056</v>
+        <v>-10.288900152052</v>
       </c>
       <c r="M21" s="18">
-        <v>48.782687105500</v>
+        <v>48.427672955974</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.979070592408</v>
+        <v>-61.043248596896</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
+        <v>3</v>
+      </c>
+      <c r="D22" s="14">
         <v>5</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
       <c r="E22" s="15">
-        <v>150</v>
+        <v>-40</v>
       </c>
       <c r="F22" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G22" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H22" s="15">
-        <v>14.285714285714</v>
+        <v>5</v>
       </c>
       <c r="I22" s="14">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J22" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K22" s="15">
-        <v>37.974683544303</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>4.807692307692</v>
+        <v>5.660377358490</v>
       </c>
       <c r="M22" s="15">
-        <v>70.3125</v>
+        <v>60</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="14">
+        <v>31</v>
+      </c>
+      <c r="D23" s="14">
+        <v>38</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-18.421052631578</v>
+      </c>
+      <c r="F23" s="14">
+        <v>125</v>
+      </c>
+      <c r="G23" s="14">
+        <v>138</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-9.420289855072</v>
+      </c>
+      <c r="I23" s="14">
+        <v>429</v>
+      </c>
+      <c r="J23" s="14">
+        <v>413</v>
+      </c>
+      <c r="K23" s="15">
+        <v>3.874092009685</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-8.723404255319</v>
+      </c>
+      <c r="M23" s="15">
+        <v>68.897637795275</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C23" s="14">
-        <v>34</v>
-      </c>
-      <c r="D23" s="14">
-        <v>39</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-12.820512820512</v>
-      </c>
-      <c r="F23" s="14">
-        <v>118</v>
-      </c>
-      <c r="G23" s="14">
-        <v>126</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-6.349206349206</v>
-      </c>
-      <c r="I23" s="14">
-        <v>398</v>
-      </c>
-      <c r="J23" s="14">
-        <v>375</v>
-      </c>
-      <c r="K23" s="15">
-        <v>6.133333333333</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-9.132420091324</v>
-      </c>
-      <c r="M23" s="15">
-        <v>65.145228215767</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="D24" s="14">
-        <v>380</v>
+        <v>333</v>
       </c>
       <c r="E24" s="15">
-        <v>-22.105263157894</v>
+        <v>-0.900900900900</v>
       </c>
       <c r="F24" s="14">
-        <v>1438</v>
+        <v>1398</v>
       </c>
       <c r="G24" s="14">
-        <v>1444</v>
+        <v>1453</v>
       </c>
       <c r="H24" s="15">
-        <v>-0.415512465373</v>
+        <v>-3.785271851342</v>
       </c>
       <c r="I24" s="14">
-        <v>4259</v>
+        <v>4597</v>
       </c>
       <c r="J24" s="14">
-        <v>4374</v>
+        <v>4707</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.629172382258</v>
+        <v>-2.336944975568</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.136948529411</v>
+        <v>-1.457663451232</v>
       </c>
       <c r="M24" s="15">
-        <v>44.667119565217</v>
+        <v>43.208722741433</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="D25" s="14">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E25" s="15">
-        <v>-28.813559322033</v>
+        <v>25</v>
       </c>
       <c r="F25" s="14">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="G25" s="14">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="H25" s="15">
-        <v>5.150214592274</v>
+        <v>5.434782608695</v>
       </c>
       <c r="I25" s="14">
-        <v>1365</v>
+        <v>1499</v>
       </c>
       <c r="J25" s="14">
-        <v>1457</v>
+        <v>1561</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.314344543582</v>
+        <v>-3.971812940422</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.968397291196</v>
+        <v>-21.477213200628</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D26" s="14">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="E26" s="15">
-        <v>1.652892561983</v>
+        <v>-0.467289719626</v>
       </c>
       <c r="F26" s="14">
-        <v>905</v>
+        <v>891</v>
       </c>
       <c r="G26" s="14">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="H26" s="15">
-        <v>1.914414414414</v>
+        <v>1.020408163265</v>
       </c>
       <c r="I26" s="14">
-        <v>2696</v>
+        <v>2904</v>
       </c>
       <c r="J26" s="14">
-        <v>2573</v>
+        <v>2787</v>
       </c>
       <c r="K26" s="15">
-        <v>4.780411970462</v>
+        <v>4.198062432723</v>
       </c>
       <c r="L26" s="15">
-        <v>0.935979034069</v>
+        <v>1.114206128133</v>
       </c>
       <c r="M26" s="15">
-        <v>6.519162386408</v>
+        <v>4.989154013015</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" s="14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E27" s="15">
-        <v>-31.25</v>
+        <v>20</v>
       </c>
       <c r="F27" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G27" s="14">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H27" s="15">
-        <v>-14.545454545454</v>
+        <v>-3.773584905660</v>
       </c>
       <c r="I27" s="14">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="J27" s="14">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="K27" s="15">
-        <v>2.808988764044</v>
+        <v>5.319148936170</v>
       </c>
       <c r="L27" s="15">
-        <v>3.389830508474</v>
+        <v>6.451612903225</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D28" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E28" s="15">
-        <v>-40</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="F28" s="14">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G28" s="14">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H28" s="15">
-        <v>1.149425287356</v>
+        <v>-7.865168539325</v>
       </c>
       <c r="I28" s="14">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="J28" s="14">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="K28" s="15">
-        <v>10.9375</v>
+        <v>8.127208480565</v>
       </c>
       <c r="L28" s="15">
-        <v>0.709219858156</v>
+        <v>-1.607717041800</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D29" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E29" s="15">
-        <v>14.285714285714</v>
+        <v>-80</v>
       </c>
       <c r="F29" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G29" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H29" s="15">
-        <v>12.5</v>
+        <v>-35</v>
       </c>
       <c r="I29" s="14">
         <v>70</v>
       </c>
       <c r="J29" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K29" s="15">
-        <v>22.807017543859</v>
+        <v>12.903225806451</v>
       </c>
       <c r="L29" s="15">
-        <v>-19.540229885057</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M29" s="15">
-        <v>-32.692307692307</v>
+        <v>-35.185185185185</v>
       </c>
       <c r="N29" s="15">
-        <v>-75.609756097561</v>
+        <v>-77.272727272727</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D30" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E30" s="15">
-        <v>16.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="F30" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G30" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="I30" s="14">
         <v>58</v>
       </c>
       <c r="J30" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K30" s="15">
-        <v>13.725490196078</v>
+        <v>5.454545454545</v>
       </c>
       <c r="L30" s="15">
-        <v>-17.142857142857</v>
+        <v>-20.547945205479</v>
       </c>
       <c r="M30" s="15">
-        <v>-35.555555555555</v>
+        <v>-38.297872340425</v>
       </c>
       <c r="N30" s="15">
-        <v>-77.519379844961</v>
+        <v>-78.985507246376</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="14">
         <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F31" s="14">
         <v>5</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I31" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="L31" s="15">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,40 +1608,40 @@
         <v>40</v>
       </c>
       <c r="C33" s="14">
-        <v>1</v>
-      </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
+        <v>2</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="14">
+        <v>3</v>
+      </c>
+      <c r="G33" s="14">
+        <v>3</v>
+      </c>
+      <c r="H33" s="15">
         <v>0</v>
       </c>
-      <c r="F33" s="14">
-        <v>2</v>
-      </c>
-      <c r="G33" s="14">
-        <v>4</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-50</v>
-      </c>
       <c r="I33" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J33" s="14">
         <v>8</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L33" s="15">
-        <v>-20</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>644</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>17862</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>9538</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>19326</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>8856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>22946</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>79825</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -199,61 +199,61 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -851,738 +851,738 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H14" s="15">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I14" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J14" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K14" s="15">
-        <v>9.090909090909</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L14" s="15">
-        <v>-4</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M14" s="15">
-        <v>-22.580645161290</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="N14" s="15">
-        <v>-82.481751824817</v>
+        <v>-82.876712328767</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D15" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E15" s="15">
-        <v>83.333333333333</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F15" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G15" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H15" s="15">
-        <v>10</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I15" s="14">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="J15" s="14">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="K15" s="15">
-        <v>13.793103448275</v>
+        <v>13.375796178343</v>
       </c>
       <c r="L15" s="15">
-        <v>38.655462184873</v>
+        <v>44.715447154471</v>
       </c>
       <c r="M15" s="15">
-        <v>117.105263157895</v>
+        <v>122.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-5.172413793103</v>
+        <v>-5.319148936170</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D16" s="14">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E16" s="15">
-        <v>-23.655913978494</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="F16" s="14">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="G16" s="14">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="H16" s="15">
-        <v>-9.036144578313</v>
+        <v>-14.005602240896</v>
       </c>
       <c r="I16" s="14">
-        <v>1032</v>
+        <v>1115</v>
       </c>
       <c r="J16" s="14">
-        <v>1136</v>
+        <v>1242</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.154929577464</v>
+        <v>-10.225442834138</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.580547112462</v>
+        <v>-21.089879688605</v>
       </c>
       <c r="M16" s="15">
-        <v>-4.884792626728</v>
+        <v>-4.700854700854</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.193370165745</v>
+        <v>-76.876814599751</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="D17" s="14">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="E17" s="15">
-        <v>-5.298013245033</v>
+        <v>8.139534883720</v>
       </c>
       <c r="F17" s="14">
-        <v>647</v>
+        <v>693</v>
       </c>
       <c r="G17" s="14">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="H17" s="15">
-        <v>-1.820940819423</v>
+        <v>3.587443946188</v>
       </c>
       <c r="I17" s="14">
-        <v>2186</v>
+        <v>2391</v>
       </c>
       <c r="J17" s="14">
-        <v>2223</v>
+        <v>2395</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.664417453891</v>
+        <v>-0.167014613778</v>
       </c>
       <c r="L17" s="15">
-        <v>6.894865525672</v>
+        <v>8.681818181818</v>
       </c>
       <c r="M17" s="15">
-        <v>90.584132519616</v>
+        <v>94.390243902439</v>
       </c>
       <c r="N17" s="15">
-        <v>1.721731037691</v>
+        <v>3.866203301476</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D18" s="14">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E18" s="15">
-        <v>-15.517241379310</v>
+        <v>-13.207547169811</v>
       </c>
       <c r="F18" s="14">
         <v>176</v>
       </c>
       <c r="G18" s="14">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H18" s="15">
-        <v>-25.106382978723</v>
+        <v>-24.786324786324</v>
       </c>
       <c r="I18" s="14">
-        <v>661</v>
+        <v>708</v>
       </c>
       <c r="J18" s="14">
-        <v>836</v>
+        <v>889</v>
       </c>
       <c r="K18" s="15">
-        <v>-20.933014354067</v>
+        <v>-20.359955005624</v>
       </c>
       <c r="L18" s="15">
-        <v>-17.786069651741</v>
+        <v>-18.055555555555</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.496437054631</v>
+        <v>-20.538720538720</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.008647798742</v>
+        <v>-87.009174311926</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D19" s="14">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="E19" s="15">
-        <v>-15.697674418604</v>
+        <v>-33.653846153846</v>
       </c>
       <c r="F19" s="14">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="G19" s="14">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="H19" s="15">
-        <v>-10.755813953488</v>
+        <v>-13.976945244956</v>
       </c>
       <c r="I19" s="14">
-        <v>2110</v>
+        <v>2254</v>
       </c>
       <c r="J19" s="14">
-        <v>2374</v>
+        <v>2582</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.120471777590</v>
+        <v>-12.703330751355</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.6</v>
+        <v>-15.422138836773</v>
       </c>
       <c r="M19" s="15">
-        <v>96.279069767441</v>
+        <v>91.341256366723</v>
       </c>
       <c r="N19" s="15">
-        <v>14.425162689804</v>
+        <v>13.437342727730</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
         <v>57</v>
       </c>
       <c r="D20" s="14">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E20" s="15">
-        <v>-39.361702127659</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="F20" s="14">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G20" s="14">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H20" s="15">
-        <v>-29.096045197740</v>
+        <v>-30.812324929972</v>
       </c>
       <c r="I20" s="14">
-        <v>902</v>
+        <v>957</v>
       </c>
       <c r="J20" s="14">
-        <v>1141</v>
+        <v>1228</v>
       </c>
       <c r="K20" s="15">
-        <v>-20.946538124452</v>
+        <v>-22.068403908794</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.712834718374</v>
+        <v>-18.274978650725</v>
       </c>
       <c r="M20" s="15">
-        <v>75.486381322957</v>
+        <v>71.813285457809</v>
       </c>
       <c r="N20" s="15">
-        <v>-78.811369509043</v>
+        <v>-79.113924050632</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>476</v>
+        <v>521</v>
       </c>
       <c r="D21" s="17">
-        <v>575</v>
+        <v>642</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.217391304347</v>
+        <v>-18.847352024922</v>
       </c>
       <c r="F21" s="17">
-        <v>2039</v>
+        <v>2074</v>
       </c>
       <c r="G21" s="17">
-        <v>2315</v>
+        <v>2362</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.922246220302</v>
+        <v>-12.193056731583</v>
       </c>
       <c r="I21" s="17">
-        <v>7080</v>
+        <v>7628</v>
       </c>
       <c r="J21" s="17">
-        <v>7877</v>
+        <v>8519</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.118065253269</v>
+        <v>-10.458974057988</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.288900152052</v>
+        <v>-9.898417198204</v>
       </c>
       <c r="M21" s="18">
-        <v>48.427672955974</v>
+        <v>48.404669260700</v>
       </c>
       <c r="N21" s="18">
-        <v>-61.043248596896</v>
+        <v>-60.835857678287</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
+        <v>11</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-81.818181818181</v>
+      </c>
+      <c r="F22" s="14">
+        <v>15</v>
+      </c>
+      <c r="G22" s="14">
+        <v>24</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-37.5</v>
+      </c>
+      <c r="I22" s="14">
+        <v>115</v>
+      </c>
+      <c r="J22" s="14">
+        <v>95</v>
+      </c>
+      <c r="K22" s="15">
+        <v>21.052631578947</v>
+      </c>
+      <c r="L22" s="15">
+        <v>2.678571428571</v>
+      </c>
+      <c r="M22" s="15">
+        <v>30.681818181818</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="C22" s="14">
-        <v>3</v>
-      </c>
-      <c r="D22" s="14">
-        <v>5</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-40</v>
-      </c>
-      <c r="F22" s="14">
-        <v>21</v>
-      </c>
-      <c r="G22" s="14">
-        <v>20</v>
-      </c>
-      <c r="H22" s="15">
-        <v>5</v>
-      </c>
-      <c r="I22" s="14">
-        <v>112</v>
-      </c>
-      <c r="J22" s="14">
-        <v>84</v>
-      </c>
-      <c r="K22" s="15">
-        <v>33.333333333333</v>
-      </c>
-      <c r="L22" s="15">
-        <v>5.660377358490</v>
-      </c>
-      <c r="M22" s="15">
-        <v>60</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D23" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E23" s="15">
-        <v>-18.421052631578</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="F23" s="14">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G23" s="14">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H23" s="15">
-        <v>-9.420289855072</v>
+        <v>-16.326530612244</v>
       </c>
       <c r="I23" s="14">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="J23" s="14">
-        <v>413</v>
+        <v>452</v>
       </c>
       <c r="K23" s="15">
-        <v>3.874092009685</v>
+        <v>0.221238938053</v>
       </c>
       <c r="L23" s="15">
-        <v>-8.723404255319</v>
+        <v>-10.650887573964</v>
       </c>
       <c r="M23" s="15">
-        <v>68.897637795275</v>
+        <v>69.029850746268</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="D24" s="14">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="E24" s="15">
-        <v>-0.900900900900</v>
+        <v>-12.188365650969</v>
       </c>
       <c r="F24" s="14">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="G24" s="14">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.785271851342</v>
+        <v>-5.209047292666</v>
       </c>
       <c r="I24" s="14">
-        <v>4597</v>
+        <v>4911</v>
       </c>
       <c r="J24" s="14">
-        <v>4707</v>
+        <v>5068</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.336944975568</v>
+        <v>-3.097868981846</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.457663451232</v>
+        <v>-1.147342995169</v>
       </c>
       <c r="M24" s="15">
-        <v>43.208722741433</v>
+        <v>41.772517321016</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="D25" s="14">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="E25" s="15">
-        <v>25</v>
+        <v>-23.770491803278</v>
       </c>
       <c r="F25" s="14">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="G25" s="14">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="H25" s="15">
-        <v>5.434782608695</v>
+        <v>1.943844492440</v>
       </c>
       <c r="I25" s="14">
-        <v>1499</v>
+        <v>1591</v>
       </c>
       <c r="J25" s="14">
-        <v>1561</v>
+        <v>1683</v>
       </c>
       <c r="K25" s="15">
-        <v>-3.971812940422</v>
+        <v>-5.466428995840</v>
       </c>
       <c r="L25" s="15">
-        <v>-21.477213200628</v>
+        <v>-21.586988664366</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>213</v>
+        <v>264</v>
       </c>
       <c r="D26" s="14">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="E26" s="15">
-        <v>-0.467289719626</v>
+        <v>36.082474226804</v>
       </c>
       <c r="F26" s="14">
-        <v>891</v>
+        <v>951</v>
       </c>
       <c r="G26" s="14">
-        <v>882</v>
+        <v>839</v>
       </c>
       <c r="H26" s="15">
-        <v>1.020408163265</v>
+        <v>13.349225268176</v>
       </c>
       <c r="I26" s="14">
-        <v>2904</v>
+        <v>3155</v>
       </c>
       <c r="J26" s="14">
-        <v>2787</v>
+        <v>2981</v>
       </c>
       <c r="K26" s="15">
-        <v>4.198062432723</v>
+        <v>5.836967460583</v>
       </c>
       <c r="L26" s="15">
-        <v>1.114206128133</v>
+        <v>3.340976089092</v>
       </c>
       <c r="M26" s="15">
-        <v>4.989154013015</v>
+        <v>6.014784946236</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E27" s="15">
-        <v>20</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F27" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G27" s="14">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H27" s="15">
-        <v>-3.773584905660</v>
+        <v>8</v>
       </c>
       <c r="I27" s="14">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="J27" s="14">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="K27" s="15">
-        <v>5.319148936170</v>
+        <v>5.970149253731</v>
       </c>
       <c r="L27" s="15">
-        <v>6.451612903225</v>
+        <v>7.035175879396</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D28" s="14">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E28" s="15">
-        <v>-18.518518518518</v>
+        <v>40</v>
       </c>
       <c r="F28" s="14">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G28" s="14">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H28" s="15">
-        <v>-7.865168539325</v>
+        <v>-6.172839506172</v>
       </c>
       <c r="I28" s="14">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="J28" s="14">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="K28" s="15">
-        <v>8.127208480565</v>
+        <v>9.060402684563</v>
       </c>
       <c r="L28" s="15">
-        <v>-1.607717041800</v>
+        <v>-4.411764705882</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E29" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F29" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G29" s="14">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H29" s="15">
-        <v>-35</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="I29" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J29" s="14">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="K29" s="15">
-        <v>12.903225806451</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-22.222222222222</v>
+        <v>-25.252525252525</v>
       </c>
       <c r="M29" s="15">
-        <v>-35.185185185185</v>
+        <v>-33.928571428571</v>
       </c>
       <c r="N29" s="15">
-        <v>-77.272727272727</v>
+        <v>-78.041543026706</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E30" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F30" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G30" s="14">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H30" s="15">
-        <v>-38.888888888888</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="I30" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J30" s="14">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="K30" s="15">
-        <v>5.454545454545</v>
+        <v>-7.462686567164</v>
       </c>
       <c r="L30" s="15">
-        <v>-20.547945205479</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="M30" s="15">
-        <v>-38.297872340425</v>
+        <v>-36.082474226804</v>
       </c>
       <c r="N30" s="15">
-        <v>-78.985507246376</v>
+        <v>-79.605263157894</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>29</v>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>5</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>29</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>400</v>
       </c>
       <c r="I31" s="14">
         <v>14</v>
       </c>
       <c r="J31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" s="15">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="L31" s="15">
         <v>75</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,40 +1608,40 @@
         <v>40</v>
       </c>
       <c r="C33" s="14">
-        <v>2</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>1</v>
+      </c>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>0</v>
       </c>
       <c r="F33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" s="14">
         <v>3</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I33" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J33" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K33" s="15">
-        <v>25</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L33" s="15">
-        <v>-9.090909090909</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>644</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>17862</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>9538</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>19326</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>8856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>22946</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>79825</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,9 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -251,9 +254,6 @@
   </si>
   <si>
     <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -851,705 +851,705 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="14">
         <v>4</v>
       </c>
       <c r="E14" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G14" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H14" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I14" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J14" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K14" s="15">
-        <v>-3.846153846153</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L14" s="15">
-        <v>-16.666666666666</v>
+        <v>-18.75</v>
       </c>
       <c r="M14" s="15">
-        <v>-26.470588235294</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N14" s="15">
-        <v>-82.876712328767</v>
+        <v>-82.894736842105</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E15" s="15">
-        <v>8.333333333333</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F15" s="14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H15" s="15">
-        <v>14.285714285714</v>
+        <v>17.5</v>
       </c>
       <c r="I15" s="14">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="J15" s="14">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="K15" s="15">
-        <v>13.375796178343</v>
+        <v>16.463414634146</v>
       </c>
       <c r="L15" s="15">
-        <v>44.715447154471</v>
+        <v>45.801526717557</v>
       </c>
       <c r="M15" s="15">
-        <v>122.5</v>
+        <v>124.705882352941</v>
       </c>
       <c r="N15" s="15">
-        <v>-5.319148936170</v>
+        <v>-8.173076923076</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D16" s="14">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E16" s="15">
-        <v>-24.528301886792</v>
+        <v>-33.684210526315</v>
       </c>
       <c r="F16" s="14">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="G16" s="14">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="H16" s="15">
-        <v>-14.005602240896</v>
+        <v>-19.518716577540</v>
       </c>
       <c r="I16" s="14">
-        <v>1115</v>
+        <v>1181</v>
       </c>
       <c r="J16" s="14">
-        <v>1242</v>
+        <v>1337</v>
       </c>
       <c r="K16" s="15">
-        <v>-10.225442834138</v>
+        <v>-11.667913238593</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.089879688605</v>
+        <v>-21.839841164791</v>
       </c>
       <c r="M16" s="15">
-        <v>-4.700854700854</v>
+        <v>-6.120826709062</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.876814599751</v>
+        <v>-76.947101307827</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D17" s="14">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E17" s="15">
-        <v>8.139534883720</v>
+        <v>-6.172839506172</v>
       </c>
       <c r="F17" s="14">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G17" s="14">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="H17" s="15">
-        <v>3.587443946188</v>
+        <v>6.298003072196</v>
       </c>
       <c r="I17" s="14">
-        <v>2391</v>
+        <v>2562</v>
       </c>
       <c r="J17" s="14">
-        <v>2395</v>
+        <v>2557</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.167014613778</v>
+        <v>0.195541650371</v>
       </c>
       <c r="L17" s="15">
-        <v>8.681818181818</v>
+        <v>9.253731343283</v>
       </c>
       <c r="M17" s="15">
-        <v>94.390243902439</v>
+        <v>95.871559633027</v>
       </c>
       <c r="N17" s="15">
-        <v>3.866203301476</v>
+        <v>3.935091277890</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D18" s="14">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E18" s="15">
-        <v>-13.207547169811</v>
+        <v>-15</v>
       </c>
       <c r="F18" s="14">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="G18" s="14">
         <v>234</v>
       </c>
       <c r="H18" s="15">
-        <v>-24.786324786324</v>
+        <v>-20.940170940170</v>
       </c>
       <c r="I18" s="14">
-        <v>708</v>
+        <v>761</v>
       </c>
       <c r="J18" s="14">
-        <v>889</v>
+        <v>949</v>
       </c>
       <c r="K18" s="15">
-        <v>-20.359955005624</v>
+        <v>-19.810326659641</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.055555555555</v>
+        <v>-16.648411829134</v>
       </c>
       <c r="M18" s="15">
-        <v>-20.538720538720</v>
+        <v>-18.347639484978</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.009174311926</v>
+        <v>-86.833910034602</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="D19" s="14">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.653846153846</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="G19" s="14">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.976945244956</v>
+        <v>-13.649425287356</v>
       </c>
       <c r="I19" s="14">
-        <v>2254</v>
+        <v>2430</v>
       </c>
       <c r="J19" s="14">
-        <v>2582</v>
+        <v>2752</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.703330751355</v>
+        <v>-11.700581395348</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.422138836773</v>
+        <v>-13.768630234208</v>
       </c>
       <c r="M19" s="15">
-        <v>91.341256366723</v>
+        <v>89.105058365758</v>
       </c>
       <c r="N19" s="15">
-        <v>13.437342727730</v>
+        <v>15.165876777251</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D20" s="14">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E20" s="15">
-        <v>-34.482758620689</v>
+        <v>-52.083333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="G20" s="14">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="H20" s="15">
-        <v>-30.812324929972</v>
+        <v>-39.772727272727</v>
       </c>
       <c r="I20" s="14">
-        <v>957</v>
+        <v>1001</v>
       </c>
       <c r="J20" s="14">
-        <v>1228</v>
+        <v>1324</v>
       </c>
       <c r="K20" s="15">
-        <v>-22.068403908794</v>
+        <v>-24.395770392749</v>
       </c>
       <c r="L20" s="15">
-        <v>-18.274978650725</v>
+        <v>-20.239043824701</v>
       </c>
       <c r="M20" s="15">
-        <v>71.813285457809</v>
+        <v>67.953020134228</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.113924050632</v>
+        <v>-79.571428571428</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>521</v>
+        <v>494</v>
       </c>
       <c r="D21" s="17">
-        <v>642</v>
+        <v>594</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.847352024922</v>
+        <v>-16.835016835016</v>
       </c>
       <c r="F21" s="17">
-        <v>2074</v>
+        <v>2042</v>
       </c>
       <c r="G21" s="17">
-        <v>2362</v>
+        <v>2359</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.193056731583</v>
+        <v>-13.437897414158</v>
       </c>
       <c r="I21" s="17">
-        <v>7628</v>
+        <v>8152</v>
       </c>
       <c r="J21" s="17">
-        <v>8519</v>
+        <v>9113</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.458974057988</v>
+        <v>-10.545374739383</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.898417198204</v>
+        <v>-9.472515269294</v>
       </c>
       <c r="M21" s="18">
-        <v>48.404669260700</v>
+        <v>48.272098945070</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.835857678287</v>
+        <v>-60.690519818690</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D22" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E22" s="15">
-        <v>-81.818181818181</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H22" s="15">
-        <v>-37.5</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="I22" s="14">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J22" s="14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K22" s="15">
-        <v>21.052631578947</v>
+        <v>20</v>
       </c>
       <c r="L22" s="15">
-        <v>2.678571428571</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>30.681818181818</v>
+        <v>22.448979591836</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="14">
+        <v>28</v>
+      </c>
+      <c r="D23" s="14">
         <v>29</v>
       </c>
-      <c r="C23" s="14">
-        <v>23</v>
-      </c>
-      <c r="D23" s="14">
-        <v>39</v>
-      </c>
       <c r="E23" s="15">
-        <v>-41.025641025641</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="F23" s="14">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G23" s="14">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H23" s="15">
-        <v>-16.326530612244</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="J23" s="14">
-        <v>452</v>
+        <v>481</v>
       </c>
       <c r="K23" s="15">
-        <v>0.221238938053</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-10.650887573964</v>
+        <v>-11.580882352941</v>
       </c>
       <c r="M23" s="15">
-        <v>69.029850746268</v>
+        <v>62.5</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="D24" s="14">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="E24" s="15">
-        <v>-12.188365650969</v>
+        <v>-8.753315649867</v>
       </c>
       <c r="F24" s="14">
-        <v>1383</v>
+        <v>1289</v>
       </c>
       <c r="G24" s="14">
-        <v>1459</v>
+        <v>1451</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.209047292666</v>
+        <v>-11.164713990351</v>
       </c>
       <c r="I24" s="14">
-        <v>4911</v>
+        <v>5248</v>
       </c>
       <c r="J24" s="14">
-        <v>5068</v>
+        <v>5445</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.097868981846</v>
+        <v>-3.617998163452</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.147342995169</v>
+        <v>-0.943752359380</v>
       </c>
       <c r="M24" s="15">
-        <v>41.772517321016</v>
+        <v>41.799513644960</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="D25" s="14">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="E25" s="15">
-        <v>-23.770491803278</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="F25" s="14">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="G25" s="14">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="H25" s="15">
-        <v>1.943844492440</v>
+        <v>-8.921161825726</v>
       </c>
       <c r="I25" s="14">
-        <v>1591</v>
+        <v>1717</v>
       </c>
       <c r="J25" s="14">
-        <v>1683</v>
+        <v>1821</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.466428995840</v>
+        <v>-5.711147721032</v>
       </c>
       <c r="L25" s="15">
-        <v>-21.586988664366</v>
+        <v>-20.250812819321</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="D26" s="14">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="E26" s="15">
-        <v>36.082474226804</v>
+        <v>0.456621004566</v>
       </c>
       <c r="F26" s="14">
-        <v>951</v>
+        <v>919</v>
       </c>
       <c r="G26" s="14">
-        <v>839</v>
+        <v>869</v>
       </c>
       <c r="H26" s="15">
-        <v>13.349225268176</v>
+        <v>5.753739930955</v>
       </c>
       <c r="I26" s="14">
-        <v>3155</v>
+        <v>3355</v>
       </c>
       <c r="J26" s="14">
-        <v>2981</v>
+        <v>3200</v>
       </c>
       <c r="K26" s="15">
-        <v>5.836967460583</v>
+        <v>4.84375</v>
       </c>
       <c r="L26" s="15">
-        <v>3.340976089092</v>
+        <v>3.357979051139</v>
       </c>
       <c r="M26" s="15">
-        <v>6.014784946236</v>
+        <v>5.469977994341</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D27" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E27" s="15">
-        <v>15.384615384615</v>
+        <v>54.545454545454</v>
       </c>
       <c r="F27" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G27" s="14">
         <v>50</v>
       </c>
       <c r="H27" s="15">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I27" s="14">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="J27" s="14">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="K27" s="15">
-        <v>5.970149253731</v>
+        <v>8.962264150943</v>
       </c>
       <c r="L27" s="15">
-        <v>7.035175879396</v>
+        <v>9.478672985781</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D28" s="14">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E28" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G28" s="14">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H28" s="15">
-        <v>-6.172839506172</v>
+        <v>-9.195402298850</v>
       </c>
       <c r="I28" s="14">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="J28" s="14">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="K28" s="15">
-        <v>9.060402684563</v>
+        <v>8.049535603715</v>
       </c>
       <c r="L28" s="15">
-        <v>-4.411764705882</v>
+        <v>-4.120879120879</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D29" s="14">
         <v>12</v>
       </c>
       <c r="E29" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F29" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" s="14">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H29" s="15">
-        <v>-39.285714285714</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J29" s="14">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-6.976744186046</v>
       </c>
       <c r="L29" s="15">
-        <v>-25.252525252525</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="M29" s="15">
-        <v>-33.928571428571</v>
+        <v>-32.203389830508</v>
       </c>
       <c r="N29" s="15">
-        <v>-78.041543026706</v>
+        <v>-77.591036414565</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E30" s="15">
-        <v>-66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F30" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G30" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H30" s="15">
-        <v>-42.307692307692</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="I30" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J30" s="14">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K30" s="15">
-        <v>-7.462686567164</v>
+        <v>-9.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-20.512820512820</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M30" s="15">
-        <v>-36.082474226804</v>
+        <v>-33.980582524271</v>
       </c>
       <c r="N30" s="15">
-        <v>-79.605263157894</v>
+        <v>-78.947368421052</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D31" s="14">
         <v>1</v>
@@ -1558,31 +1558,31 @@
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="I31" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="L31" s="15">
-        <v>75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1610,38 +1610,38 @@
       <c r="C33" s="14">
         <v>1</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>0</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="I33" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J33" s="14">
         <v>9</v>
       </c>
       <c r="K33" s="15">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L33" s="15">
-        <v>-26.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>644</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>17862</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>9538</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>19326</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>8856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>22946</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>79825</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -199,61 +199,61 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
+    <t>Shooting Inc.</t>
+  </si>
+  <si>
+    <t>Hate Crimes</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>Shooting Inc.</t>
-  </si>
-  <si>
-    <t>Hate Crimes</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -851,720 +851,720 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>2</v>
       </c>
       <c r="D14" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F14" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H14" s="15">
-        <v>-66.666666666666</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="I14" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J14" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K14" s="15">
-        <v>-13.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="L14" s="15">
-        <v>-18.75</v>
+        <v>-20</v>
       </c>
       <c r="M14" s="15">
-        <v>-23.529411764705</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="N14" s="15">
-        <v>-82.894736842105</v>
+        <v>-82.389937106918</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D15" s="14">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E15" s="15">
-        <v>71.428571428571</v>
+        <v>-40</v>
       </c>
       <c r="F15" s="14">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G15" s="14">
         <v>40</v>
       </c>
       <c r="H15" s="15">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="I15" s="14">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="J15" s="14">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="K15" s="15">
-        <v>16.463414634146</v>
+        <v>12.290502793296</v>
       </c>
       <c r="L15" s="15">
-        <v>45.801526717557</v>
+        <v>42.553191489361</v>
       </c>
       <c r="M15" s="15">
-        <v>124.705882352941</v>
+        <v>128.409090909091</v>
       </c>
       <c r="N15" s="15">
-        <v>-8.173076923076</v>
+        <v>-9.459459459459</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D16" s="14">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.684210526315</v>
+        <v>-30.973451327433</v>
       </c>
       <c r="F16" s="14">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G16" s="14">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="H16" s="15">
-        <v>-19.518716577540</v>
+        <v>-25.798525798525</v>
       </c>
       <c r="I16" s="14">
-        <v>1181</v>
+        <v>1263</v>
       </c>
       <c r="J16" s="14">
-        <v>1337</v>
+        <v>1450</v>
       </c>
       <c r="K16" s="15">
-        <v>-11.667913238593</v>
+        <v>-12.896551724137</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.839841164791</v>
+        <v>-20.963704630788</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.120826709062</v>
+        <v>-6.305637982195</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.947101307827</v>
+        <v>-76.641390789717</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="D17" s="14">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E17" s="15">
-        <v>-6.172839506172</v>
+        <v>5.421686746987</v>
       </c>
       <c r="F17" s="14">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="G17" s="14">
         <v>651</v>
       </c>
       <c r="H17" s="15">
-        <v>6.298003072196</v>
+        <v>5.222734254992</v>
       </c>
       <c r="I17" s="14">
-        <v>2562</v>
+        <v>2747</v>
       </c>
       <c r="J17" s="14">
-        <v>2557</v>
+        <v>2723</v>
       </c>
       <c r="K17" s="15">
-        <v>0.195541650371</v>
+        <v>0.881380829966</v>
       </c>
       <c r="L17" s="15">
-        <v>9.253731343283</v>
+        <v>9.704472843450</v>
       </c>
       <c r="M17" s="15">
-        <v>95.871559633027</v>
+        <v>96.635647816750</v>
       </c>
       <c r="N17" s="15">
-        <v>3.935091277890</v>
+        <v>3.076923076923</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D18" s="14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E18" s="15">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="G18" s="14">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="H18" s="15">
-        <v>-20.940170940170</v>
+        <v>-9.292035398230</v>
       </c>
       <c r="I18" s="14">
-        <v>761</v>
+        <v>819</v>
       </c>
       <c r="J18" s="14">
-        <v>949</v>
+        <v>1004</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.810326659641</v>
+        <v>-18.426294820717</v>
       </c>
       <c r="L18" s="15">
-        <v>-16.648411829134</v>
+        <v>-14.509394572025</v>
       </c>
       <c r="M18" s="15">
-        <v>-18.347639484978</v>
+        <v>-16.086065573770</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.833910034602</v>
+        <v>-86.667751912746</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D19" s="14">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-16.751269035533</v>
       </c>
       <c r="F19" s="14">
-        <v>601</v>
+        <v>626</v>
       </c>
       <c r="G19" s="14">
-        <v>696</v>
+        <v>747</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.649425287356</v>
+        <v>-16.198125836680</v>
       </c>
       <c r="I19" s="14">
-        <v>2430</v>
+        <v>2602</v>
       </c>
       <c r="J19" s="14">
-        <v>2752</v>
+        <v>2949</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.700581395348</v>
+        <v>-11.766700576466</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.768630234208</v>
+        <v>-13.237745915305</v>
       </c>
       <c r="M19" s="15">
-        <v>89.105058365758</v>
+        <v>90.204678362573</v>
       </c>
       <c r="N19" s="15">
-        <v>15.165876777251</v>
+        <v>13.823272090988</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D20" s="14">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="E20" s="15">
-        <v>-52.083333333333</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F20" s="14">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G20" s="14">
-        <v>352</v>
+        <v>391</v>
       </c>
       <c r="H20" s="15">
-        <v>-39.772727272727</v>
+        <v>-43.989769820971</v>
       </c>
       <c r="I20" s="14">
-        <v>1001</v>
+        <v>1065</v>
       </c>
       <c r="J20" s="14">
-        <v>1324</v>
+        <v>1438</v>
       </c>
       <c r="K20" s="15">
-        <v>-24.395770392749</v>
+        <v>-25.938803894297</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.239043824701</v>
+        <v>-19.561933534743</v>
       </c>
       <c r="M20" s="15">
-        <v>67.953020134228</v>
+        <v>63.594470046082</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.571428571428</v>
+        <v>-79.499518768046</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>494</v>
+        <v>549</v>
       </c>
       <c r="D21" s="17">
-        <v>594</v>
+        <v>662</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.835016835016</v>
+        <v>-17.069486404833</v>
       </c>
       <c r="F21" s="17">
-        <v>2042</v>
+        <v>2086</v>
       </c>
       <c r="G21" s="17">
-        <v>2359</v>
+        <v>2473</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.437897414158</v>
+        <v>-15.649009300444</v>
       </c>
       <c r="I21" s="17">
-        <v>8152</v>
+        <v>8725</v>
       </c>
       <c r="J21" s="17">
-        <v>9113</v>
+        <v>9775</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.545374739383</v>
+        <v>-10.741687979539</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.472515269294</v>
+        <v>-8.724762004393</v>
       </c>
       <c r="M21" s="18">
-        <v>48.272098945070</v>
+        <v>48.839986352780</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.690519818690</v>
+        <v>-60.479231779680</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D22" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F22" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G22" s="14">
         <v>23</v>
       </c>
       <c r="H22" s="15">
-        <v>-30.434782608695</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="I22" s="14">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J22" s="14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K22" s="15">
-        <v>20</v>
+        <v>25.490196078431</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>0.787401574803</v>
       </c>
       <c r="M22" s="15">
-        <v>22.448979591836</v>
+        <v>20.754716981132</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D23" s="14">
         <v>29</v>
       </c>
       <c r="E23" s="15">
-        <v>-3.448275862068</v>
+        <v>13.793103448275</v>
       </c>
       <c r="F23" s="14">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G23" s="14">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H23" s="15">
-        <v>-20</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="I23" s="14">
-        <v>481</v>
+        <v>517</v>
       </c>
       <c r="J23" s="14">
-        <v>481</v>
+        <v>510</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>1.372549019607</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.580882352941</v>
+        <v>-9.773123909249</v>
       </c>
       <c r="M23" s="15">
-        <v>62.5</v>
+        <v>62.578616352201</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="D24" s="14">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="E24" s="15">
-        <v>-8.753315649867</v>
+        <v>2.234636871508</v>
       </c>
       <c r="F24" s="14">
-        <v>1289</v>
+        <v>1354</v>
       </c>
       <c r="G24" s="14">
-        <v>1451</v>
+        <v>1429</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.164713990351</v>
+        <v>-5.248425472358</v>
       </c>
       <c r="I24" s="14">
-        <v>5248</v>
+        <v>5619</v>
       </c>
       <c r="J24" s="14">
-        <v>5445</v>
+        <v>5803</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.617998163452</v>
+        <v>-3.170773737721</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.943752359380</v>
+        <v>0.375133976420</v>
       </c>
       <c r="M24" s="15">
-        <v>41.799513644960</v>
+        <v>43.195718654434</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D25" s="14">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="E25" s="15">
-        <v>-8.695652173913</v>
+        <v>6.034482758620</v>
       </c>
       <c r="F25" s="14">
-        <v>439</v>
+        <v>477</v>
       </c>
       <c r="G25" s="14">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H25" s="15">
-        <v>-8.921161825726</v>
+        <v>-0.625</v>
       </c>
       <c r="I25" s="14">
-        <v>1717</v>
+        <v>1843</v>
       </c>
       <c r="J25" s="14">
-        <v>1821</v>
+        <v>1937</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.711147721032</v>
+        <v>-4.852865255549</v>
       </c>
       <c r="L25" s="15">
-        <v>-20.250812819321</v>
+        <v>-18.738977072310</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D26" s="14">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="E26" s="15">
-        <v>0.456621004566</v>
+        <v>1.680672268907</v>
       </c>
       <c r="F26" s="14">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="G26" s="14">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="H26" s="15">
-        <v>5.753739930955</v>
+        <v>5.780346820809</v>
       </c>
       <c r="I26" s="14">
-        <v>3355</v>
+        <v>3594</v>
       </c>
       <c r="J26" s="14">
-        <v>3200</v>
+        <v>3438</v>
       </c>
       <c r="K26" s="15">
-        <v>4.84375</v>
+        <v>4.537521815008</v>
       </c>
       <c r="L26" s="15">
-        <v>3.357979051139</v>
+        <v>3.842819994221</v>
       </c>
       <c r="M26" s="15">
-        <v>5.469977994341</v>
+        <v>5.488699735837</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
+        <v>12</v>
+      </c>
+      <c r="D27" s="14">
         <v>17</v>
       </c>
-      <c r="D27" s="14">
-        <v>11</v>
-      </c>
       <c r="E27" s="15">
-        <v>54.545454545454</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F27" s="14">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G27" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H27" s="15">
-        <v>14</v>
+        <v>9.803921568627</v>
       </c>
       <c r="I27" s="14">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="J27" s="14">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="K27" s="15">
-        <v>8.962264150943</v>
+        <v>5.676855895196</v>
       </c>
       <c r="L27" s="15">
-        <v>9.478672985781</v>
+        <v>6.607929515418</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D28" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="F28" s="14">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G28" s="14">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H28" s="15">
-        <v>-9.195402298850</v>
+        <v>-8.163265306122</v>
       </c>
       <c r="I28" s="14">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="J28" s="14">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="K28" s="15">
-        <v>8.049535603715</v>
+        <v>4.802259887005</v>
       </c>
       <c r="L28" s="15">
-        <v>-4.120879120879</v>
+        <v>-6.075949367088</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D29" s="14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E29" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="F29" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G29" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>-60.606060606060</v>
       </c>
       <c r="I29" s="14">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J29" s="14">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K29" s="15">
-        <v>-6.976744186046</v>
+        <v>-8.888888888888</v>
       </c>
       <c r="L29" s="15">
-        <v>-24.528301886792</v>
+        <v>-28.070175438596</v>
       </c>
       <c r="M29" s="15">
-        <v>-32.203389830508</v>
+        <v>-35.9375</v>
       </c>
       <c r="N29" s="15">
-        <v>-77.591036414565</v>
+        <v>-78.249336870026</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D30" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E30" s="15">
         <v>-25</v>
       </c>
       <c r="F30" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G30" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H30" s="15">
-        <v>-43.333333333333</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="I30" s="14">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J30" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K30" s="15">
-        <v>-9.333333333333</v>
+        <v>-11.392405063291</v>
       </c>
       <c r="L30" s="15">
-        <v>-19.047619047619</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.980582524271</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N30" s="15">
-        <v>-78.947368421052</v>
+        <v>-79.411764705882</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>15</v>
@@ -1576,13 +1576,13 @@
         <v>150</v>
       </c>
       <c r="L31" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1611,37 +1611,37 @@
         <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F33" s="14">
         <v>5</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="I33" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J33" s="14">
         <v>9</v>
       </c>
       <c r="K33" s="15">
-        <v>33.333333333333</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L33" s="15">
-        <v>-20</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>644</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>17862</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>9538</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>19326</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>8856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>22946</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>79825</v>

--- a/data/source/weekly/cs-en-us-pbbx.xlsx
+++ b/data/source/weekly/cs-en-us-pbbx.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,9 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -251,9 +254,6 @@
   </si>
   <si>
     <t>Hate Crimes</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Traffic Statistics</t>
@@ -851,738 +851,738 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>2</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="14">
         <v>2</v>
       </c>
       <c r="E14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>3</v>
       </c>
       <c r="G14" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H14" s="15">
-        <v>-72.727272727272</v>
+        <v>-75</v>
       </c>
       <c r="I14" s="14">
         <v>28</v>
       </c>
       <c r="J14" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K14" s="15">
-        <v>-12.5</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L14" s="15">
-        <v>-20</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M14" s="15">
-        <v>-17.647058823529</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="N14" s="15">
-        <v>-82.389937106918</v>
+        <v>-83.431952662721</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D15" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" s="15">
-        <v>-40</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F15" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H15" s="15">
-        <v>15</v>
+        <v>-2.083333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="J15" s="14">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="K15" s="15">
-        <v>12.290502793296</v>
+        <v>10.880829015544</v>
       </c>
       <c r="L15" s="15">
-        <v>42.553191489361</v>
+        <v>41.721854304635</v>
       </c>
       <c r="M15" s="15">
-        <v>128.409090909091</v>
+        <v>120.618556701031</v>
       </c>
       <c r="N15" s="15">
-        <v>-9.459459459459</v>
+        <v>-10.084033613445</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D16" s="14">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E16" s="15">
-        <v>-30.973451327433</v>
+        <v>-37.719298245614</v>
       </c>
       <c r="F16" s="14">
         <v>302</v>
       </c>
       <c r="G16" s="14">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="H16" s="15">
-        <v>-25.798525798525</v>
+        <v>-29.439252336448</v>
       </c>
       <c r="I16" s="14">
-        <v>1263</v>
+        <v>1336</v>
       </c>
       <c r="J16" s="14">
-        <v>1450</v>
+        <v>1564</v>
       </c>
       <c r="K16" s="15">
-        <v>-12.896551724137</v>
+        <v>-14.578005115089</v>
       </c>
       <c r="L16" s="15">
-        <v>-20.963704630788</v>
+        <v>-21.040189125295</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.305637982195</v>
+        <v>-7.093184979137</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.641390789717</v>
+        <v>-76.639272600104</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="D17" s="14">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E17" s="15">
-        <v>5.421686746987</v>
+        <v>-8.888888888888</v>
       </c>
       <c r="F17" s="14">
-        <v>685</v>
+        <v>701</v>
       </c>
       <c r="G17" s="14">
-        <v>651</v>
+        <v>680</v>
       </c>
       <c r="H17" s="15">
-        <v>5.222734254992</v>
+        <v>3.088235294117</v>
       </c>
       <c r="I17" s="14">
-        <v>2747</v>
+        <v>2926</v>
       </c>
       <c r="J17" s="14">
-        <v>2723</v>
+        <v>2903</v>
       </c>
       <c r="K17" s="15">
-        <v>0.881380829966</v>
+        <v>0.792283844299</v>
       </c>
       <c r="L17" s="15">
-        <v>9.704472843450</v>
+        <v>8.894678079642</v>
       </c>
       <c r="M17" s="15">
-        <v>96.635647816750</v>
+        <v>95.327102803738</v>
       </c>
       <c r="N17" s="15">
-        <v>3.076923076923</v>
+        <v>2.379286214135</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D18" s="14">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>5.128205128205</v>
       </c>
       <c r="F18" s="14">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G18" s="14">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="H18" s="15">
-        <v>-9.292035398230</v>
+        <v>-3.864734299516</v>
       </c>
       <c r="I18" s="14">
-        <v>819</v>
+        <v>862</v>
       </c>
       <c r="J18" s="14">
-        <v>1004</v>
+        <v>1043</v>
       </c>
       <c r="K18" s="15">
-        <v>-18.426294820717</v>
+        <v>-17.353787152444</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.509394572025</v>
+        <v>-14.399205561072</v>
       </c>
       <c r="M18" s="15">
-        <v>-16.086065573770</v>
+        <v>-16.472868217054</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.667751912746</v>
+        <v>-86.766963463309</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D19" s="14">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E19" s="15">
-        <v>-16.751269035533</v>
+        <v>-23.762376237623</v>
       </c>
       <c r="F19" s="14">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="G19" s="14">
-        <v>747</v>
+        <v>777</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.198125836680</v>
+        <v>-18.404118404118</v>
       </c>
       <c r="I19" s="14">
-        <v>2602</v>
+        <v>2772</v>
       </c>
       <c r="J19" s="14">
-        <v>2949</v>
+        <v>3151</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.766700576466</v>
+        <v>-12.027927642018</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.237745915305</v>
+        <v>-12.72040302267</v>
       </c>
       <c r="M19" s="15">
-        <v>90.204678362573</v>
+        <v>89.993145990404</v>
       </c>
       <c r="N19" s="15">
-        <v>13.823272090988</v>
+        <v>13.050570962479</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D20" s="14">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="E20" s="15">
-        <v>-42.105263157894</v>
+        <v>-30.337078651685</v>
       </c>
       <c r="F20" s="14">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G20" s="14">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="H20" s="15">
-        <v>-43.989769820971</v>
+        <v>-41.191709844559</v>
       </c>
       <c r="I20" s="14">
-        <v>1065</v>
+        <v>1127</v>
       </c>
       <c r="J20" s="14">
-        <v>1438</v>
+        <v>1527</v>
       </c>
       <c r="K20" s="15">
-        <v>-25.938803894297</v>
+        <v>-26.195153896529</v>
       </c>
       <c r="L20" s="15">
-        <v>-19.561933534743</v>
+        <v>-19.957386363636</v>
       </c>
       <c r="M20" s="15">
-        <v>63.594470046082</v>
+        <v>62.626262626262</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.499518768046</v>
+        <v>-79.501636958894</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>549</v>
+        <v>504</v>
       </c>
       <c r="D21" s="17">
-        <v>662</v>
+        <v>640</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.069486404833</v>
+        <v>-21.25</v>
       </c>
       <c r="F21" s="17">
-        <v>2086</v>
+        <v>2113</v>
       </c>
       <c r="G21" s="17">
-        <v>2473</v>
+        <v>2538</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.649009300444</v>
+        <v>-16.745468873128</v>
       </c>
       <c r="I21" s="17">
-        <v>8725</v>
+        <v>9265</v>
       </c>
       <c r="J21" s="17">
-        <v>9775</v>
+        <v>10415</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.741687979539</v>
+        <v>-11.041766682669</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.724762004393</v>
+        <v>-8.800078747908</v>
       </c>
       <c r="M21" s="18">
-        <v>48.839986352780</v>
+        <v>48.145187080268</v>
       </c>
       <c r="N21" s="18">
-        <v>-60.479231779680</v>
+        <v>-60.487035141589</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="14">
+        <v>3</v>
+      </c>
+      <c r="D22" s="14">
+        <v>9</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F22" s="14">
+        <v>18</v>
+      </c>
+      <c r="G22" s="14">
         <v>27</v>
       </c>
-      <c r="C22" s="14">
-        <v>8</v>
-      </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>300</v>
-      </c>
-      <c r="F22" s="14">
-        <v>19</v>
-      </c>
-      <c r="G22" s="14">
-        <v>23</v>
-      </c>
       <c r="H22" s="15">
-        <v>-17.391304347826</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J22" s="14">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K22" s="15">
-        <v>25.490196078431</v>
+        <v>18.018018018018</v>
       </c>
       <c r="L22" s="15">
-        <v>0.787401574803</v>
+        <v>-0.757575757575</v>
       </c>
       <c r="M22" s="15">
-        <v>20.754716981132</v>
+        <v>11.965811965812</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="14">
+        <v>18</v>
+      </c>
+      <c r="D23" s="14">
+        <v>36</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F23" s="14">
+        <v>103</v>
+      </c>
+      <c r="G23" s="14">
+        <v>133</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-22.556390977443</v>
+      </c>
+      <c r="I23" s="14">
+        <v>535</v>
+      </c>
+      <c r="J23" s="14">
+        <v>546</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-2.014652014652</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-11.716171617161</v>
+      </c>
+      <c r="M23" s="15">
+        <v>54.624277456647</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C23" s="14">
-        <v>33</v>
-      </c>
-      <c r="D23" s="14">
-        <v>29</v>
-      </c>
-      <c r="E23" s="15">
-        <v>13.793103448275</v>
-      </c>
-      <c r="F23" s="14">
-        <v>115</v>
-      </c>
-      <c r="G23" s="14">
-        <v>135</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-14.814814814814</v>
-      </c>
-      <c r="I23" s="14">
-        <v>517</v>
-      </c>
-      <c r="J23" s="14">
-        <v>510</v>
-      </c>
-      <c r="K23" s="15">
-        <v>1.372549019607</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-9.773123909249</v>
-      </c>
-      <c r="M23" s="15">
-        <v>62.578616352201</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>366</v>
+        <v>339</v>
       </c>
       <c r="D24" s="14">
-        <v>358</v>
+        <v>313</v>
       </c>
       <c r="E24" s="15">
-        <v>2.234636871508</v>
+        <v>8.306709265175</v>
       </c>
       <c r="F24" s="14">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="G24" s="14">
-        <v>1429</v>
+        <v>1409</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.248425472358</v>
+        <v>-3.548616039744</v>
       </c>
       <c r="I24" s="14">
-        <v>5619</v>
+        <v>5952</v>
       </c>
       <c r="J24" s="14">
-        <v>5803</v>
+        <v>6116</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.170773737721</v>
+        <v>-2.681491170699</v>
       </c>
       <c r="L24" s="15">
-        <v>0.375133976420</v>
+        <v>0.932677632694</v>
       </c>
       <c r="M24" s="15">
-        <v>43.195718654434</v>
+        <v>41.917024320457</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="D25" s="14">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="E25" s="15">
-        <v>6.034482758620</v>
+        <v>9.890109890109</v>
       </c>
       <c r="F25" s="14">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="G25" s="14">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="H25" s="15">
-        <v>-0.625</v>
+        <v>-4.282655246252</v>
       </c>
       <c r="I25" s="14">
-        <v>1843</v>
+        <v>1945</v>
       </c>
       <c r="J25" s="14">
-        <v>1937</v>
+        <v>2028</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.852865255549</v>
+        <v>-4.092702169625</v>
       </c>
       <c r="L25" s="15">
-        <v>-18.738977072310</v>
+        <v>-18.482816429170</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="D26" s="14">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="E26" s="15">
-        <v>1.680672268907</v>
+        <v>-3.603603603603</v>
       </c>
       <c r="F26" s="14">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="G26" s="14">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="H26" s="15">
-        <v>5.780346820809</v>
+        <v>5.612829324169</v>
       </c>
       <c r="I26" s="14">
-        <v>3594</v>
+        <v>3802</v>
       </c>
       <c r="J26" s="14">
-        <v>3438</v>
+        <v>3660</v>
       </c>
       <c r="K26" s="15">
-        <v>4.537521815008</v>
+        <v>3.879781420765</v>
       </c>
       <c r="L26" s="15">
-        <v>3.842819994221</v>
+        <v>3.063160748170</v>
       </c>
       <c r="M26" s="15">
-        <v>5.488699735837</v>
+        <v>3.596730245231</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
         <v>12</v>
       </c>
       <c r="D27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E27" s="15">
-        <v>-29.411764705882</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F27" s="14">
         <v>56</v>
       </c>
       <c r="G27" s="14">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H27" s="15">
-        <v>9.803921568627</v>
+        <v>-5.084745762711</v>
       </c>
       <c r="I27" s="14">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="J27" s="14">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="K27" s="15">
-        <v>5.676855895196</v>
+        <v>3.238866396761</v>
       </c>
       <c r="L27" s="15">
-        <v>6.607929515418</v>
+        <v>6.25</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D28" s="14">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E28" s="15">
-        <v>-22.580645161290</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G28" s="14">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H28" s="15">
-        <v>-8.163265306122</v>
+        <v>-2.150537634408</v>
       </c>
       <c r="I28" s="14">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="J28" s="14">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="K28" s="15">
-        <v>4.802259887005</v>
+        <v>4.255319148936</v>
       </c>
       <c r="L28" s="15">
-        <v>-6.075949367088</v>
+        <v>-7.547169811320</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E29" s="15">
-        <v>-25</v>
+        <v>-87.5</v>
       </c>
       <c r="F29" s="14">
         <v>13</v>
       </c>
       <c r="G29" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H29" s="15">
-        <v>-60.606060606060</v>
+        <v>-63.888888888888</v>
       </c>
       <c r="I29" s="14">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J29" s="14">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K29" s="15">
-        <v>-8.888888888888</v>
+        <v>-15.306122448979</v>
       </c>
       <c r="L29" s="15">
-        <v>-28.070175438596</v>
+        <v>-30.833333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-35.9375</v>
+        <v>-41.134751773049</v>
       </c>
       <c r="N29" s="15">
-        <v>-78.249336870026</v>
+        <v>-79.706601466992</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E30" s="15">
-        <v>-25</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F30" s="14">
         <v>13</v>
       </c>
       <c r="G30" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H30" s="15">
-        <v>-53.571428571428</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="I30" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J30" s="14">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K30" s="15">
-        <v>-11.392405063291</v>
+        <v>-16.470588235294</v>
       </c>
       <c r="L30" s="15">
-        <v>-23.076923076923</v>
+        <v>-26.041666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-36.363636363636</v>
+        <v>-39.316239316239</v>
       </c>
       <c r="N30" s="15">
-        <v>-79.411764705882</v>
+        <v>-80.758807588075</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="13" t="s">
         <v>38</v>
       </c>
+      <c r="C31" s="14">
+        <v>3</v>
+      </c>
       <c r="D31" s="13" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J31" s="14">
         <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L31" s="15">
-        <v>50</v>
+        <v>63.636363636363</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
         <v>1</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>28</v>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="I33" s="14">
         <v>13</v>
       </c>
       <c r="J33" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K33" s="15">
-        <v>44.444444444444</v>
+        <v>30</v>
       </c>
       <c r="L33" s="15">
-        <v>-13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>644</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>17862</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>9538</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>19326</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>8856</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>22946</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>79825</v>
